--- a/output/multipliers_table_port.xlsx
+++ b/output/multipliers_table_port.xlsx
@@ -2901,16 +2901,16 @@
         <v>1</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.79</v>
+        <v>-0.82</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -2930,16 +2930,16 @@
         <v>2</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
         <v>0.01</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="I96" t="n">
         <v>0.04</v>
@@ -2962,13 +2962,13 @@
         <v>-0.13</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2977,10 +2977,10 @@
         <v>0.02</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="I97" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="98">
@@ -2988,16 +2988,16 @@
         <v>4</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="D98" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0.02</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="I98" t="n">
         <v>0.05</v>
@@ -3020,13 +3020,13 @@
         <v>-0.12</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="D99" t="n">
         <v>0.05</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.75</v>
+        <v>-0.79</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3035,10 +3035,10 @@
         <v>0.03</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="I99" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -3096,13 +3096,13 @@
         <v>-0</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="D102" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="E102" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="F102" t="n">
         <v>-0.01</v>
@@ -3114,7 +3114,7 @@
         <v>0.01</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="103">
@@ -3125,19 +3125,19 @@
         <v>-0</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="E103" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="F103" t="n">
         <v>-0.04</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="H103" t="n">
         <v>0.01</v>
@@ -3154,19 +3154,19 @@
         <v>-0.01</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="D104" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="H104" t="n">
         <v>0.01</v>
@@ -3183,22 +3183,22 @@
         <v>-0.01</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="D105" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E105" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I105" t="n">
         <v>-0.01</v>
@@ -3218,7 +3218,7 @@
         <v>0.31</v>
       </c>
       <c r="E106" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="F106" t="n">
         <v>-0.1</v>
@@ -3227,7 +3227,7 @@
         <v>-0.12</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I106" t="n">
         <v>-0.01</v>
@@ -3290,31 +3290,31 @@
         <v>1</v>
       </c>
       <c r="B109" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="D109" t="n">
         <v>-0.14</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F109" t="n">
         <v>0.01</v>
       </c>
       <c r="G109" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I109" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.74</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="110">
@@ -3325,7 +3325,7 @@
         <v>0.24</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="D110" t="n">
         <v>-0.09</v>
@@ -3337,16 +3337,16 @@
         <v>0.04</v>
       </c>
       <c r="G110" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H110" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.11</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="111">
@@ -3357,28 +3357,28 @@
         <v>0.24</v>
       </c>
       <c r="C111" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E111" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="D111" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="E111" t="n">
-        <v>-0.22</v>
       </c>
       <c r="F111" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G111" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I111" t="n">
         <v>0.32</v>
       </c>
-      <c r="H111" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0.31</v>
-      </c>
       <c r="J111" t="n">
-        <v>-1.46</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="112">
@@ -3386,31 +3386,31 @@
         <v>4</v>
       </c>
       <c r="B112" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="F112" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G112" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H112" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.81</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="113">
@@ -3421,28 +3421,28 @@
         <v>0.19</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F113" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G113" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H113" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.14</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="116">
@@ -12601,16 +12601,16 @@
         <v>1</v>
       </c>
       <c r="B95" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C95" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D95" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E95" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -12630,16 +12630,16 @@
         <v>2</v>
       </c>
       <c r="B96" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C96" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E96" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -12648,7 +12648,7 @@
         <v>-0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I96" t="n">
         <v>-0</v>
@@ -12662,13 +12662,13 @@
         <v>0.04</v>
       </c>
       <c r="C97" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D97" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -12677,10 +12677,10 @@
         <v>-0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="98">
@@ -12688,16 +12688,16 @@
         <v>4</v>
       </c>
       <c r="B98" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E98" t="n">
         <v>0.02</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.05</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -12706,7 +12706,7 @@
         <v>-0.01</v>
       </c>
       <c r="H98" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I98" t="n">
         <v>-0.04</v>
@@ -12720,13 +12720,13 @@
         <v>0.02</v>
       </c>
       <c r="C99" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
         <v>0.16</v>
       </c>
       <c r="E99" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -12735,10 +12735,10 @@
         <v>-0.01</v>
       </c>
       <c r="H99" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="101">
@@ -12796,13 +12796,13 @@
         <v>-0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D102" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F102" t="n">
         <v>0.01</v>
@@ -12814,7 +12814,7 @@
         <v>-0.01</v>
       </c>
       <c r="I102" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -12825,25 +12825,25 @@
         <v>-0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D103" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F103" t="n">
         <v>0.01</v>
       </c>
       <c r="G103" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H103" t="n">
         <v>-0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="104">
@@ -12854,19 +12854,19 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D104" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F104" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>-0</v>
@@ -12883,22 +12883,22 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D105" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F105" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G105" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -12918,7 +12918,7 @@
         <v>0.05</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F106" t="n">
         <v>0.03</v>
@@ -12927,7 +12927,7 @@
         <v>0.02</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -12990,31 +12990,31 @@
         <v>1</v>
       </c>
       <c r="B109" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C109" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D109" t="n">
         <v>0.02</v>
       </c>
       <c r="E109" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F109" t="n">
         <v>-0.01</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="110">
@@ -13025,7 +13025,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D110" t="n">
         <v>0.06</v>
@@ -13037,16 +13037,16 @@
         <v>-0.01</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H110" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I110" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I110" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="J110" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="111">
@@ -13057,28 +13057,28 @@
         <v>0.08</v>
       </c>
       <c r="C111" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D111" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E111" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F111" t="n">
         <v>-0</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H111" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I111" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I111" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="J111" t="n">
-        <v>-0.43</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="112">
@@ -13086,31 +13086,31 @@
         <v>4</v>
       </c>
       <c r="B112" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C112" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D112" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E112" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.53</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="113">
@@ -13121,28 +13121,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D113" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="E113" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F113" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H113" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G113" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="I113" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.62</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="116">

--- a/output/multipliers_table_port.xlsx
+++ b/output/multipliers_table_port.xlsx
@@ -611,7 +611,7 @@
         <v>0.03</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="E7" t="n">
         <v>-0.01</v>
@@ -899,7 +899,7 @@
         <v>-0.66</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>-1.91</v>
@@ -934,7 +934,7 @@
         <v>-0.01</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="19">
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="E19" t="n">
         <v>0.21</v>
@@ -966,7 +966,7 @@
         <v>-0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="20">
@@ -995,10 +995,10 @@
         <v>-0.22</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1030,7 +1030,7 @@
         <v>-0.12</v>
       </c>
       <c r="J21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="24">
@@ -1188,7 +1188,7 @@
         <v>-0.34</v>
       </c>
       <c r="E29" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F29" t="n">
         <v>3.93</v>
@@ -1214,10 +1214,10 @@
         <v>-0.03</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
       <c r="E30" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F30" t="n">
         <v>3.93</v>
@@ -1415,7 +1415,7 @@
         <v>0.51</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H37" t="n">
         <v>-0.01</v>
@@ -1502,7 +1502,7 @@
         <v>-0.66</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>-1.91</v>
@@ -1537,7 +1537,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.58</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="42">
@@ -1557,19 +1557,19 @@
         <v>1.16</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="G42" t="n">
         <v>0.08</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
       <c r="I42" t="n">
         <v>-0.77</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="43">
@@ -1577,13 +1577,13 @@
         <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="C43" t="n">
         <v>1.27</v>
       </c>
       <c r="D43" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="E43" t="n">
         <v>1.14</v>
@@ -1595,13 +1595,13 @@
         <v>0.05</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="J43" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="44">
@@ -1612,10 +1612,10 @@
         <v>1.36</v>
       </c>
       <c r="C44" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D44" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="E44" t="n">
         <v>1.1</v>
@@ -1627,13 +1627,13 @@
         <v>0.04</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.07</v>
+        <v>-1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="47">
@@ -1788,7 +1788,7 @@
         <v>-0.28</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.76</v>
+        <v>-2.75</v>
       </c>
       <c r="E52" t="n">
         <v>-0.29</v>
@@ -1803,7 +1803,7 @@
         <v>-0.67</v>
       </c>
       <c r="I52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
@@ -1811,13 +1811,13 @@
         <v>5</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="C53" t="n">
         <v>-0.29</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.94</v>
+        <v>-2.93</v>
       </c>
       <c r="E53" t="n">
         <v>-0.33</v>
@@ -1832,7 +1832,7 @@
         <v>-0.85</v>
       </c>
       <c r="I53" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="55">
@@ -2108,7 +2108,7 @@
         <v>1.03</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="64">
@@ -2140,7 +2140,7 @@
         <v>1.22</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="65">
@@ -2157,7 +2157,7 @@
         <v>-0.55</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="F65" t="n">
         <v>0.17</v>
@@ -2172,7 +2172,7 @@
         <v>1.15</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.09</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="66">
@@ -2204,7 +2204,7 @@
         <v>1.12</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.99</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="67">
@@ -2215,7 +2215,7 @@
         <v>-0.91</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.75</v>
+        <v>-0.74</v>
       </c>
       <c r="D67" t="n">
         <v>-0.88</v>
@@ -2236,7 +2236,7 @@
         <v>1.14</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.96</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="70">
@@ -2406,7 +2406,7 @@
         <v>-0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="76">
@@ -2426,7 +2426,7 @@
         <v>-2.07</v>
       </c>
       <c r="F76" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0.08</v>
@@ -2621,7 +2621,7 @@
         <v>-0.27</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="H83" t="n">
         <v>0.01</v>
@@ -2743,7 +2743,7 @@
         <v>0.68</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="88">
@@ -2775,7 +2775,7 @@
         <v>0.71</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.13</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="89">
@@ -2807,7 +2807,7 @@
         <v>0.75</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.14</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="90">
@@ -2815,13 +2815,13 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="C90" t="n">
         <v>-0.52</v>
       </c>
       <c r="D90" t="n">
-        <v>-2.73</v>
+        <v>-2.72</v>
       </c>
       <c r="E90" t="n">
         <v>-0.5600000000000001</v>
@@ -2833,13 +2833,13 @@
         <v>0.83</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I90" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.1</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="93">
@@ -2968,7 +2968,7 @@
         <v>-0.05</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.68</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
         <v>-0.13</v>
       </c>
       <c r="D104" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="E104" t="n">
         <v>0.63</v>
@@ -3325,7 +3325,7 @@
         <v>0.24</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="D110" t="n">
         <v>-0.09</v>
@@ -3372,7 +3372,7 @@
         <v>0.33</v>
       </c>
       <c r="H111" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I111" t="n">
         <v>0.32</v>
@@ -3421,10 +3421,10 @@
         <v>0.19</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="E113" t="n">
         <v>-0.24</v>
@@ -3436,13 +3436,13 @@
         <v>0.33</v>
       </c>
       <c r="H113" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I113" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.22</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="116">
@@ -3620,16 +3620,16 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="C122" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="D122" t="n">
         <v>15.12</v>
       </c>
       <c r="E122" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>-1.85</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="124">
@@ -3740,7 +3740,7 @@
         <v>-0.03</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="H126" t="n">
         <v>0.04</v>
@@ -3818,10 +3818,10 @@
         <v>-0.87</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.05</v>
+        <v>-1.04</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.75</v>
+        <v>-0.74</v>
       </c>
       <c r="F129" t="n">
         <v>-0.02</v>
@@ -3917,7 +3917,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="133">
@@ -3949,7 +3949,7 @@
         <v>0.19</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.22</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="134">
@@ -3957,7 +3957,7 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="C134" t="n">
         <v>2.5</v>
@@ -3981,7 +3981,7 @@
         <v>0.36</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.93</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="135">
@@ -4004,7 +4004,7 @@
         <v>0.21</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="H135" t="n">
         <v>0.82</v>
@@ -4013,7 +4013,7 @@
         <v>0.57</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.05</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="136">
@@ -4021,13 +4021,13 @@
         <v>5</v>
       </c>
       <c r="B136" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="C136" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="D136" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E136" t="n">
         <v>4.35</v>
@@ -4036,16 +4036,16 @@
         <v>0.28</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="H136" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I136" t="n">
         <v>0.82</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.83</v>
       </c>
     </row>
     <row r="139">
@@ -4203,7 +4203,7 @@
         <v>-0.22</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="F144" t="n">
         <v>-0</v>
@@ -4630,7 +4630,7 @@
         <v>-1.07</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="E159" t="n">
         <v>-0.32</v>
@@ -4648,7 +4648,7 @@
         <v>-0.39</v>
       </c>
       <c r="J159" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="162">
@@ -5172,7 +5172,7 @@
         <v>0.21</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="F180" t="n">
         <v>-0.33</v>
@@ -5184,7 +5184,7 @@
         <v>-0.6</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="J180" t="n">
         <v>2.78</v>
@@ -5219,7 +5219,7 @@
         <v>-0.28</v>
       </c>
       <c r="J181" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="182">
@@ -5230,7 +5230,7 @@
         <v>-0.65</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.31</v>
+        <v>-1.3</v>
       </c>
       <c r="D182" t="n">
         <v>0.61</v>
@@ -5245,13 +5245,13 @@
         <v>-0.16</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="I182" t="n">
         <v>-0.25</v>
       </c>
       <c r="J182" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
     </row>
   </sheetData>
@@ -10311,7 +10311,7 @@
         <v>0.01</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E7" t="n">
         <v>0.02</v>
@@ -10599,7 +10599,7 @@
         <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J17" t="n">
         <v>-0.02</v>
@@ -10634,7 +10634,7 @@
         <v>-0.05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19">
@@ -10645,10 +10645,10 @@
         <v>-0.01</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="E19" t="n">
         <v>-0.01</v>
@@ -10666,7 +10666,7 @@
         <v>-0.05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -10695,10 +10695,10 @@
         <v>-0.06</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="21">
@@ -10730,7 +10730,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="24">
@@ -10888,7 +10888,7 @@
         <v>-0.08</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="F29" t="n">
         <v>-0.47</v>
@@ -10914,10 +10914,10 @@
         <v>-0.03</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F30" t="n">
         <v>-0.49</v>
@@ -11115,7 +11115,7 @@
         <v>-0.03</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="H37" t="n">
         <v>0.01</v>
@@ -11202,7 +11202,7 @@
         <v>0.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J40" t="n">
         <v>-0.02</v>
@@ -11237,7 +11237,7 @@
         <v>0.02</v>
       </c>
       <c r="J41" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="42">
@@ -11257,19 +11257,19 @@
         <v>-0.02</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G42" t="n">
         <v>0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I42" t="n">
         <v>0.01</v>
       </c>
       <c r="J42" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="43">
@@ -11277,13 +11277,13 @@
         <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C43" t="n">
         <v>-0.02</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="E43" t="n">
         <v>-0.02</v>
@@ -11295,13 +11295,13 @@
         <v>0.02</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J43" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="44">
@@ -11312,10 +11312,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="E44" t="n">
         <v>-0.03</v>
@@ -11327,13 +11327,13 @@
         <v>0.04</v>
       </c>
       <c r="H44" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="47">
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="E52" t="n">
         <v>-0.01</v>
@@ -11497,13 +11497,13 @@
         <v>-0</v>
       </c>
       <c r="G52" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0.04</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="53">
@@ -11511,13 +11511,13 @@
         <v>5</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="C53" t="n">
         <v>-0</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.47</v>
+        <v>-0.46</v>
       </c>
       <c r="E53" t="n">
         <v>-0.03</v>
@@ -11532,7 +11532,7 @@
         <v>0.05</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="55">
@@ -11651,7 +11651,7 @@
         <v>-0.04</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E58" t="n">
         <v>-0.01</v>
@@ -11808,7 +11808,7 @@
         <v>0.04</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="64">
@@ -11840,7 +11840,7 @@
         <v>0.23</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.35</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="65">
@@ -11857,7 +11857,7 @@
         <v>-0.04</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="F65" t="n">
         <v>0.02</v>
@@ -11872,7 +11872,7 @@
         <v>0.16</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.01</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="66">
@@ -11904,7 +11904,7 @@
         <v>0.12</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.69</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="67">
@@ -11915,7 +11915,7 @@
         <v>-0.05</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D67" t="n">
         <v>-0.06</v>
@@ -11936,7 +11936,7 @@
         <v>0.14</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.34</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="70">
@@ -12106,7 +12106,7 @@
         <v>0.21</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="76">
@@ -12126,7 +12126,7 @@
         <v>0.26</v>
       </c>
       <c r="F76" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>-0.02</v>
@@ -12321,7 +12321,7 @@
         <v>0.05</v>
       </c>
       <c r="G83" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H83" t="n">
         <v>-0</v>
@@ -12443,7 +12443,7 @@
         <v>-0.18</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="88">
@@ -12475,7 +12475,7 @@
         <v>-0.21</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="89">
@@ -12507,7 +12507,7 @@
         <v>-0.22</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.88</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -12515,13 +12515,13 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="C90" t="n">
         <v>0.15</v>
       </c>
       <c r="D90" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="E90" t="n">
         <v>0.11</v>
@@ -12533,13 +12533,13 @@
         <v>-0.2</v>
       </c>
       <c r="H90" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I90" t="n">
         <v>-0.22</v>
       </c>
-      <c r="I90" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="J90" t="n">
-        <v>-1.13</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="93">
@@ -12668,7 +12668,7 @@
         <v>0.13</v>
       </c>
       <c r="E97" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -12720,7 +12720,7 @@
         <v>0.02</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D99" t="n">
         <v>0.16</v>
@@ -12857,7 +12857,7 @@
         <v>0.03</v>
       </c>
       <c r="D104" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E104" t="n">
         <v>-0.02</v>
@@ -13025,7 +13025,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D110" t="n">
         <v>0.06</v>
@@ -13072,7 +13072,7 @@
         <v>-0.02</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I111" t="n">
         <v>-0.05</v>
@@ -13121,10 +13121,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E113" t="n">
         <v>0.05</v>
@@ -13136,13 +13136,13 @@
         <v>-0.03</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="116">
@@ -13320,16 +13320,16 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="C122" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="D122" t="n">
         <v>1.7</v>
       </c>
       <c r="E122" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
@@ -13440,7 +13440,7 @@
         <v>0.01</v>
       </c>
       <c r="G126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>-0.01</v>
@@ -13518,10 +13518,10 @@
         <v>0.24</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E129" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F129" t="n">
         <v>0.06</v>
@@ -13617,7 +13617,7 @@
         <v>-0.03</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="133">
@@ -13649,7 +13649,7 @@
         <v>-0.09</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="134">
@@ -13657,7 +13657,7 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C134" t="n">
         <v>0.11</v>
@@ -13681,7 +13681,7 @@
         <v>-0.14</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="135">
@@ -13704,7 +13704,7 @@
         <v>0.06</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="H135" t="n">
         <v>-0.28</v>
@@ -13713,7 +13713,7 @@
         <v>-0.16</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="136">
@@ -13721,13 +13721,13 @@
         <v>5</v>
       </c>
       <c r="B136" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="C136" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="D136" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="E136" t="n">
         <v>0.24</v>
@@ -13736,16 +13736,16 @@
         <v>0.09</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
       <c r="I136" t="n">
         <v>-0.16</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.59</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="139">
@@ -13903,7 +13903,7 @@
         <v>0.18</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="F144" t="n">
         <v>-0</v>
@@ -14330,7 +14330,7 @@
         <v>-0.14</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="E159" t="n">
         <v>-0.17</v>
@@ -14348,7 +14348,7 @@
         <v>-0.14</v>
       </c>
       <c r="J159" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="162">
@@ -14872,7 +14872,7 @@
         <v>-0.24</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F180" t="n">
         <v>-0.02</v>
@@ -14884,7 +14884,7 @@
         <v>-0.04</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="J180" t="n">
         <v>0.78</v>
@@ -14919,7 +14919,7 @@
         <v>-0.09</v>
       </c>
       <c r="J181" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="182">
@@ -14930,7 +14930,7 @@
         <v>-0.05</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="D182" t="n">
         <v>-0.23</v>
@@ -14945,13 +14945,13 @@
         <v>-0.04</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I182" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/multipliers_table_port.xlsx
+++ b/output/multipliers_table_port.xlsx
@@ -524,7 +524,7 @@
         <v>-0.08</v>
       </c>
       <c r="D4" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E4" t="n">
         <v>0.04</v>
@@ -582,7 +582,7 @@
         <v>-0.06</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="E6" t="n">
         <v>-0.13</v>
@@ -608,13 +608,13 @@
         <v>-0.12</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -716,7 +716,7 @@
         <v>-0.12</v>
       </c>
       <c r="D11" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="E11" t="n">
         <v>0.21</v>
@@ -797,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>-0.12</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v>0.67</v>
       </c>
       <c r="E17" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="F17" t="n">
         <v>-0.16</v>
@@ -899,7 +899,7 @@
         <v>-0.66</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="J17" t="n">
         <v>-1.91</v>
@@ -913,7 +913,7 @@
         <v>0.14</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D18" t="n">
         <v>0.3</v>
@@ -931,10 +931,10 @@
         <v>-0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="J18" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="19">
@@ -948,7 +948,7 @@
         <v>-0.16</v>
       </c>
       <c r="D19" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E19" t="n">
         <v>0.21</v>
@@ -963,7 +963,7 @@
         <v>-0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J19" t="n">
         <v>0.75</v>
@@ -989,10 +989,10 @@
         <v>-0.15</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="I20" t="n">
         <v>-0.13</v>
@@ -1009,7 +1009,7 @@
         <v>0.01</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="D21" t="n">
         <v>0.17</v>
@@ -1021,10 +1021,10 @@
         <v>-0.15</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="I21" t="n">
         <v>-0.12</v>
@@ -1127,7 +1127,7 @@
         <v>0.12</v>
       </c>
       <c r="D27" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="E27" t="n">
         <v>0.5</v>
@@ -1156,7 +1156,7 @@
         <v>0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E28" t="n">
         <v>0.38</v>
@@ -1185,10 +1185,10 @@
         <v>-0.04</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="E29" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F29" t="n">
         <v>3.93</v>
@@ -1374,7 +1374,7 @@
         <v>0.02</v>
       </c>
       <c r="C36" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="D36" t="n">
         <v>0.85</v>
@@ -1412,10 +1412,10 @@
         <v>0.75</v>
       </c>
       <c r="F37" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G37" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H37" t="n">
         <v>-0.01</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
         <v>0.67</v>
       </c>
       <c r="E40" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="F40" t="n">
         <v>-0.16</v>
@@ -1502,7 +1502,7 @@
         <v>-0.66</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="J40" t="n">
         <v>-1.91</v>
@@ -1513,7 +1513,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="C41" t="n">
         <v>1.67</v>
@@ -1528,16 +1528,16 @@
         <v>-0.26</v>
       </c>
       <c r="G41" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.59</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="42">
@@ -1557,19 +1557,19 @@
         <v>1.16</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="G42" t="n">
         <v>0.08</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="I42" t="n">
         <v>-0.77</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="43">
@@ -1583,10 +1583,10 @@
         <v>1.27</v>
       </c>
       <c r="D43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="E43" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F43" t="n">
         <v>-0.53</v>
@@ -1595,13 +1595,13 @@
         <v>0.05</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="J43" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="44">
@@ -1609,16 +1609,16 @@
         <v>5</v>
       </c>
       <c r="B44" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="C44" t="n">
         <v>1.08</v>
       </c>
       <c r="D44" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="F44" t="n">
         <v>-0.67</v>
@@ -1627,13 +1627,13 @@
         <v>0.04</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.06</v>
+        <v>-1.07</v>
       </c>
       <c r="I44" t="n">
         <v>-0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="47">
@@ -1695,25 +1695,25 @@
         <v>1</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
       <c r="C49" t="n">
         <v>-0.11</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.06</v>
+        <v>-1</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="F49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="I49" t="n">
         <v>-0.01</v>
@@ -1724,25 +1724,25 @@
         <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.94</v>
+        <v>-1.63</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="F50" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0.01</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="I50" t="n">
         <v>0.03</v>
@@ -1753,25 +1753,25 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.49</v>
+        <v>-0.4</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.46</v>
+        <v>-2.02</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.26</v>
+        <v>-0.21</v>
       </c>
       <c r="F51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0.02</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.47</v>
+        <v>-0.4</v>
       </c>
       <c r="I51" t="n">
         <v>0.05</v>
@@ -1782,28 +1782,28 @@
         <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.51</v>
+        <v>-0.41</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.75</v>
+        <v>-2.24</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="F52" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.67</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="53">
@@ -1811,28 +1811,28 @@
         <v>5</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.5</v>
+        <v>-0.41</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.93</v>
+        <v>-2.37</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="F53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="I53" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="55">
@@ -1890,10 +1890,10 @@
         <v>-0.01</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E56" t="n">
         <v>-0.03</v>
@@ -1919,19 +1919,19 @@
         <v>-0.03</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="F57" t="n">
         <v>-0.05</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H57" t="n">
         <v>0.02</v>
@@ -1945,28 +1945,28 @@
         <v>3</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.42</v>
+        <v>-0.34</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="H58" t="n">
         <v>0.02</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="59">
@@ -1974,22 +1974,22 @@
         <v>4</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="H59" t="n">
         <v>0.02</v>
@@ -2003,28 +2003,28 @@
         <v>5</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3</v>
+        <v>-0.23</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="F60" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G60" t="n">
         <v>-0.24</v>
       </c>
-      <c r="G60" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="H60" t="n">
         <v>0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="62">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -2084,31 +2084,31 @@
         <v>1</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="F63" t="n">
         <v>0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="H63" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="I63" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="64">
@@ -2116,31 +2116,31 @@
         <v>2</v>
       </c>
       <c r="B64" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C64" t="n">
         <v>-0.53</v>
       </c>
-      <c r="C64" t="n">
-        <v>-0.64</v>
-      </c>
       <c r="D64" t="n">
-        <v>-0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="F64" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G64" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="H64" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>1.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="65">
@@ -2148,31 +2148,31 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.76</v>
+        <v>-0.62</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.55</v>
+        <v>-0.47</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.52</v>
+        <v>-0.44</v>
       </c>
       <c r="F65" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="G65" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="H65" t="n">
-        <v>1.15</v>
+        <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.15</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="66">
@@ -2180,31 +2180,31 @@
         <v>4</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.83</v>
+        <v>-0.68</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.78</v>
+        <v>-0.63</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.73</v>
+        <v>-0.61</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.68</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="G66" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="H66" t="n">
-        <v>1.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.08</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="67">
@@ -2212,31 +2212,31 @@
         <v>5</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.91</v>
+        <v>-0.74</v>
       </c>
       <c r="C67" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="D67" t="n">
         <v>-0.74</v>
       </c>
-      <c r="D67" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="E67" t="n">
-        <v>-0.79</v>
+        <v>-0.65</v>
       </c>
       <c r="F67" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="G67" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1.22</v>
+        <v>0.98</v>
       </c>
       <c r="I67" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.11</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="70">
@@ -2301,13 +2301,13 @@
         <v>-0.62</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.07</v>
+        <v>-1.08</v>
       </c>
       <c r="D72" t="n">
         <v>-0.09</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.18</v>
+        <v>-2.21</v>
       </c>
       <c r="F72" t="n">
         <v>-0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="I72" t="n">
         <v>-0.02</v>
@@ -2327,16 +2327,16 @@
         <v>2</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="C73" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.18</v>
+        <v>-2.22</v>
       </c>
       <c r="F73" t="n">
         <v>-0</v>
@@ -2356,16 +2356,16 @@
         <v>3</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.93</v>
+        <v>-0.95</v>
       </c>
       <c r="D74" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E74" t="n">
-        <v>-2.11</v>
+        <v>-2.16</v>
       </c>
       <c r="F74" t="n">
         <v>-0</v>
@@ -2374,7 +2374,7 @@
         <v>0.04</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="I74" t="n">
         <v>0.09</v>
@@ -2385,16 +2385,16 @@
         <v>4</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.91</v>
+        <v>-0.93</v>
       </c>
       <c r="D75" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.05</v>
+        <v>-2.1</v>
       </c>
       <c r="F75" t="n">
         <v>-0</v>
@@ -2403,10 +2403,10 @@
         <v>0.06</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.85</v>
+        <v>-0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="76">
@@ -2414,16 +2414,16 @@
         <v>5</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.02</v>
+        <v>-1.05</v>
       </c>
       <c r="D76" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.07</v>
+        <v>-2.12</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0.08</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.01</v>
+        <v>-1.03</v>
       </c>
       <c r="I76" t="n">
         <v>0.18</v>
@@ -2493,7 +2493,7 @@
         <v>-0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="D79" t="n">
         <v>-0.1</v>
@@ -2522,13 +2522,13 @@
         <v>-0</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="D80" t="n">
         <v>-0.24</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="F80" t="n">
         <v>-0.11</v>
@@ -2548,22 +2548,22 @@
         <v>3</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="F81" t="n">
         <v>-0.19</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="H81" t="n">
         <v>0.02</v>
@@ -2580,19 +2580,19 @@
         <v>0.01</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="F82" t="n">
         <v>-0.24</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="H82" t="n">
         <v>0.01</v>
@@ -2609,19 +2609,19 @@
         <v>0.02</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="H83" t="n">
         <v>0.01</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -2687,13 +2687,13 @@
         <v>1</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="D86" t="n">
-        <v>-2.3</v>
+        <v>-2.33</v>
       </c>
       <c r="E86" t="n">
         <v>-0.3</v>
@@ -2702,16 +2702,16 @@
         <v>0.09</v>
       </c>
       <c r="G86" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H86" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="J86" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="87">
@@ -2719,31 +2719,31 @@
         <v>2</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.74</v>
+        <v>-0.76</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.85</v>
+        <v>-0.86</v>
       </c>
       <c r="D87" t="n">
-        <v>-2.46</v>
+        <v>-2.5</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="F87" t="n">
         <v>0.15</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H87" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="I87" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="88">
@@ -2751,31 +2751,31 @@
         <v>3</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="D88" t="n">
-        <v>-2.55</v>
+        <v>-2.61</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="F88" t="n">
         <v>0.22</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H88" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.09</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="89">
@@ -2783,31 +2783,31 @@
         <v>4</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.66</v>
+        <v>-0.68</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.55</v>
+        <v>-0.57</v>
       </c>
       <c r="D89" t="n">
-        <v>-2.62</v>
+        <v>-2.68</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.57</v>
+        <v>-0.59</v>
       </c>
       <c r="F89" t="n">
         <v>0.3</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.07</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="90">
@@ -2815,31 +2815,31 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="D90" t="n">
-        <v>-2.72</v>
+        <v>-2.8</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="F90" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="G90" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H90" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.98</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="93">
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="I95" t="n">
         <v>-0.01</v>
@@ -2994,7 +2994,7 @@
         <v>-0.31</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E98" t="n">
         <v>-0.73</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="C99" t="n">
         <v>-0.37</v>
@@ -3035,7 +3035,7 @@
         <v>0.03</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="I99" t="n">
         <v>0.07000000000000001</v>
@@ -3221,7 +3221,7 @@
         <v>0.58</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="G106" t="n">
         <v>-0.12</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
         <v>0.01</v>
       </c>
       <c r="G109" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H109" t="n">
         <v>0.31</v>
@@ -3340,10 +3340,10 @@
         <v>0.33</v>
       </c>
       <c r="H110" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="I110" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J110" t="n">
         <v>-1.15</v>
@@ -3404,7 +3404,7 @@
         <v>0.33</v>
       </c>
       <c r="H112" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="I112" t="n">
         <v>0.33</v>
@@ -3427,7 +3427,7 @@
         <v>-0.32</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F113" t="n">
         <v>0.13</v>
@@ -3442,7 +3442,7 @@
         <v>0.34</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.2</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="116">
@@ -3539,7 +3539,7 @@
         <v>0.76</v>
       </c>
       <c r="D119" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="E119" t="n">
         <v>1.31</v>
@@ -3620,10 +3620,10 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="C122" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D122" t="n">
         <v>15.12</v>
@@ -3821,7 +3821,7 @@
         <v>-1.04</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="F129" t="n">
         <v>-0.02</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I132" t="n">
         <v>0.07000000000000001</v>
@@ -3943,10 +3943,10 @@
         <v>-0.15</v>
       </c>
       <c r="H133" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I133" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J133" t="n">
         <v>-2.23</v>
@@ -3957,7 +3957,7 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="C134" t="n">
         <v>2.5</v>
@@ -3975,13 +3975,13 @@
         <v>-0.22</v>
       </c>
       <c r="H134" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I134" t="n">
         <v>0.36</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.96</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="135">
@@ -4021,13 +4021,13 @@
         <v>5</v>
       </c>
       <c r="B136" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="C136" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
       <c r="D136" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="E136" t="n">
         <v>4.35</v>
@@ -4042,10 +4042,10 @@
         <v>1.14</v>
       </c>
       <c r="I136" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.83</v>
+        <v>-8.84</v>
       </c>
     </row>
     <row r="139">
@@ -4113,7 +4113,7 @@
         <v>-0.42</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="E141" t="n">
         <v>-0.68</v>
@@ -4142,7 +4142,7 @@
         <v>-0.36</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="E142" t="n">
         <v>-0.6</v>
@@ -4171,7 +4171,7 @@
         <v>-0.35</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="E143" t="n">
         <v>-0.65</v>
@@ -4183,7 +4183,7 @@
         <v>-0.32</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="I143" t="n">
         <v>0.01</v>
@@ -4200,7 +4200,7 @@
         <v>-0.33</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="E144" t="n">
         <v>-0.66</v>
@@ -4212,7 +4212,7 @@
         <v>-0.31</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="I144" t="n">
         <v>0.04</v>
@@ -4223,13 +4223,13 @@
         <v>5</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E145" t="n">
         <v>-0.67</v>
@@ -4241,7 +4241,7 @@
         <v>-0.3</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="I145" t="n">
         <v>0.07000000000000001</v>
@@ -4389,10 +4389,10 @@
         <v>-0.03</v>
       </c>
       <c r="C151" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="D151" t="n">
         <v>-0.26</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-0.25</v>
       </c>
       <c r="E151" t="n">
         <v>-0.06</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
         <v>-0.34</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.66</v>
+        <v>-0.67</v>
       </c>
       <c r="D155" t="n">
         <v>-0.15</v>
@@ -4514,7 +4514,7 @@
         <v>-0.06</v>
       </c>
       <c r="H155" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="I155" t="n">
         <v>-0.28</v>
@@ -4537,22 +4537,22 @@
         <v>-0.17</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="F156" t="n">
         <v>-0.51</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="I156" t="n">
         <v>-0.32</v>
       </c>
       <c r="J156" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="157">
@@ -4560,7 +4560,7 @@
         <v>3</v>
       </c>
       <c r="B157" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="C157" t="n">
         <v>-0.9399999999999999</v>
@@ -4569,22 +4569,22 @@
         <v>-0.31</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="F157" t="n">
         <v>-0.67</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="J157" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="158">
@@ -4592,31 +4592,31 @@
         <v>4</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="C158" t="n">
-        <v>-1</v>
+        <v>-1.01</v>
       </c>
       <c r="D158" t="n">
         <v>-0.41</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="F158" t="n">
         <v>-0.71</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="J158" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="159">
@@ -4624,7 +4624,7 @@
         <v>5</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="C159" t="n">
         <v>-1.07</v>
@@ -4633,22 +4633,22 @@
         <v>-0.51</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="F159" t="n">
         <v>-0.74</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="I159" t="n">
         <v>-0.39</v>
       </c>
       <c r="J159" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="162">
@@ -4745,7 +4745,7 @@
         <v>0.11</v>
       </c>
       <c r="D165" t="n">
-        <v>-2.22</v>
+        <v>-2.23</v>
       </c>
       <c r="E165" t="n">
         <v>-0.53</v>
@@ -4774,7 +4774,7 @@
         <v>0.25</v>
       </c>
       <c r="D166" t="n">
-        <v>-2.82</v>
+        <v>-2.84</v>
       </c>
       <c r="E166" t="n">
         <v>-0.31</v>
@@ -4800,10 +4800,10 @@
         <v>-0.37</v>
       </c>
       <c r="C167" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="D167" t="n">
-        <v>-3.28</v>
+        <v>-3.3</v>
       </c>
       <c r="E167" t="n">
         <v>-0.07000000000000001</v>
@@ -4815,7 +4815,7 @@
         <v>-0.12</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="I167" t="n">
         <v>-0.71</v>
@@ -4826,16 +4826,16 @@
         <v>5</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
       <c r="C168" t="n">
         <v>0.46</v>
       </c>
       <c r="D168" t="n">
-        <v>-3.67</v>
+        <v>-3.69</v>
       </c>
       <c r="E168" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F168" t="n">
         <v>-0</v>
@@ -4844,7 +4844,7 @@
         <v>-0.11</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="I168" t="n">
         <v>-0.7</v>
@@ -4963,7 +4963,7 @@
         <v>-0.09</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="D173" t="n">
         <v>-0.19</v>
@@ -4989,10 +4989,10 @@
         <v>4</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="D174" t="n">
         <v>-0.25</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -5146,13 +5146,13 @@
         <v>-0.25</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="J179" t="n">
         <v>1.81</v>
@@ -5163,7 +5163,7 @@
         <v>3</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="C180" t="n">
         <v>-1.17</v>
@@ -5172,22 +5172,22 @@
         <v>0.21</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="F180" t="n">
         <v>-0.33</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="J180" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="181">
@@ -5195,10 +5195,10 @@
         <v>4</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="C181" t="n">
-        <v>-1.26</v>
+        <v>-1.27</v>
       </c>
       <c r="D181" t="n">
         <v>0.4</v>
@@ -5210,16 +5210,16 @@
         <v>-0.39</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="J181" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="182">
@@ -5227,31 +5227,31 @@
         <v>5</v>
       </c>
       <c r="B182" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E182" t="n">
         <v>-0.65</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E182" t="n">
-        <v>-0.64</v>
       </c>
       <c r="F182" t="n">
         <v>-0.43</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="J182" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
     </row>
   </sheetData>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
         <v>-0.02</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E4" t="n">
         <v>-0.05</v>
@@ -10282,7 +10282,7 @@
         <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
         <v>0.02</v>
@@ -10308,13 +10308,13 @@
         <v>0.02</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -10416,7 +10416,7 @@
         <v>-0.02</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
         <v>-0.01</v>
@@ -10497,7 +10497,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0.02</v>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
         <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="F17" t="n">
         <v>-0.02</v>
@@ -10599,7 +10599,7 @@
         <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J17" t="n">
         <v>-0.02</v>
@@ -10613,7 +10613,7 @@
         <v>-0.02</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>-0.04</v>
@@ -10631,10 +10631,10 @@
         <v>-0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="19">
@@ -10648,7 +10648,7 @@
         <v>-0.02</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
         <v>-0.01</v>
@@ -10663,7 +10663,7 @@
         <v>-0.04</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="J19" t="n">
         <v>0.3</v>
@@ -10689,10 +10689,10 @@
         <v>-0.01</v>
       </c>
       <c r="G20" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H20" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.06</v>
       </c>
       <c r="I20" t="n">
         <v>-0.05</v>
@@ -10709,7 +10709,7 @@
         <v>0.02</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
@@ -10721,10 +10721,10 @@
         <v>-0.02</v>
       </c>
       <c r="G21" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H21" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.06</v>
       </c>
       <c r="I21" t="n">
         <v>-0.07000000000000001</v>
@@ -10827,7 +10827,7 @@
         <v>-0.04</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E27" t="n">
         <v>-0.07000000000000001</v>
@@ -10856,7 +10856,7 @@
         <v>-0.03</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
         <v>-0.08</v>
@@ -10885,10 +10885,10 @@
         <v>-0.02</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="F29" t="n">
         <v>-0.47</v>
@@ -11074,7 +11074,7 @@
         <v>-0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D36" t="n">
         <v>0.03</v>
@@ -11112,10 +11112,10 @@
         <v>-0.01</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H37" t="n">
         <v>0.01</v>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
         <v>-0.04</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="F40" t="n">
         <v>-0.02</v>
@@ -11202,7 +11202,7 @@
         <v>0.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J40" t="n">
         <v>-0.02</v>
@@ -11213,7 +11213,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C41" t="n">
         <v>-0.02</v>
@@ -11228,16 +11228,16 @@
         <v>0.01</v>
       </c>
       <c r="G41" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J41" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="42">
@@ -11257,19 +11257,19 @@
         <v>-0.02</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G42" t="n">
         <v>0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I42" t="n">
         <v>0.01</v>
       </c>
       <c r="J42" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43">
@@ -11283,10 +11283,10 @@
         <v>-0.02</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F43" t="n">
         <v>0.01</v>
@@ -11295,13 +11295,13 @@
         <v>0.02</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J43" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="44">
@@ -11309,16 +11309,16 @@
         <v>5</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C44" t="n">
         <v>-0.03</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F44" t="n">
         <v>0.01</v>
@@ -11327,13 +11327,13 @@
         <v>0.04</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0.01</v>
       </c>
       <c r="J44" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -11395,25 +11395,25 @@
         <v>1</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C49" t="n">
         <v>0.01</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.16</v>
+        <v>-0.1</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I49" t="n">
         <v>-0.01</v>
@@ -11424,25 +11424,25 @@
         <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.37</v>
+        <v>-0.06</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F50" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>-0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="I50" t="n">
         <v>0.03</v>
@@ -11453,25 +11453,25 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.41</v>
+        <v>0.03</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I51" t="n">
         <v>0.02</v>
@@ -11482,28 +11482,28 @@
         <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E52" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F52" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="I52" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="53">
@@ -11511,28 +11511,28 @@
         <v>5</v>
       </c>
       <c r="B53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I53" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-0.01</v>
       </c>
     </row>
     <row r="55">
@@ -11590,10 +11590,10 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E56" t="n">
         <v>-0</v>
@@ -11616,28 +11616,28 @@
         <v>2</v>
       </c>
       <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H57" t="n">
         <v>-0</v>
       </c>
-      <c r="C57" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
       <c r="I57" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -11645,28 +11645,28 @@
         <v>3</v>
       </c>
       <c r="B58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H58" t="n">
         <v>-0</v>
       </c>
-      <c r="C58" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="I58" t="n">
         <v>-0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0.01</v>
       </c>
     </row>
     <row r="59">
@@ -11674,28 +11674,28 @@
         <v>4</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="E59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G59" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F59" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G59" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I59" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -11703,28 +11703,28 @@
         <v>5</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.05</v>
+        <v>-0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="62">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -11784,31 +11784,31 @@
         <v>1</v>
       </c>
       <c r="B63" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C63" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="H63" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.6</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -11816,31 +11816,31 @@
         <v>2</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="C64" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G64" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D64" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.26</v>
-      </c>
       <c r="H64" t="n">
-        <v>0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.37</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="65">
@@ -11848,31 +11848,31 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.03</v>
+        <v>0.11</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="H65" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.16</v>
+        <v>-0.08</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.07</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="66">
@@ -11880,31 +11880,31 @@
         <v>4</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="D66" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G66" t="n">
         <v>-0.06</v>
       </c>
-      <c r="E66" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0.18</v>
-      </c>
       <c r="H66" t="n">
-        <v>0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="I66" t="n">
-        <v>0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.78</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="67">
@@ -11912,31 +11912,31 @@
         <v>5</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.01</v>
+        <v>0.14</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="F67" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.49</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="70">
@@ -12001,13 +12001,13 @@
         <v>0.02</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D72" t="n">
         <v>0.02</v>
       </c>
       <c r="E72" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="F72" t="n">
         <v>-0</v>
@@ -12016,7 +12016,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>-0.02</v>
@@ -12027,16 +12027,16 @@
         <v>2</v>
       </c>
       <c r="B73" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D73" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="F73" t="n">
         <v>-0</v>
@@ -12056,16 +12056,16 @@
         <v>3</v>
       </c>
       <c r="B74" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C74" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D74" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="E74" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="F74" t="n">
         <v>-0</v>
@@ -12074,7 +12074,7 @@
         <v>-0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I74" t="n">
         <v>-0.03</v>
@@ -12085,16 +12085,16 @@
         <v>4</v>
       </c>
       <c r="B75" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D75" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="E75" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="F75" t="n">
         <v>-0</v>
@@ -12103,10 +12103,10 @@
         <v>-0.02</v>
       </c>
       <c r="H75" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -12114,16 +12114,16 @@
         <v>5</v>
       </c>
       <c r="B76" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D76" t="n">
         <v>0.46</v>
       </c>
       <c r="E76" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -12132,7 +12132,7 @@
         <v>-0.02</v>
       </c>
       <c r="H76" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I76" t="n">
         <v>-0.09</v>
@@ -12193,7 +12193,7 @@
         <v>-0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -12222,13 +12222,13 @@
         <v>-0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D80" t="n">
         <v>0.02</v>
       </c>
       <c r="E80" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F80" t="n">
         <v>-0</v>
@@ -12237,7 +12237,7 @@
         <v>-0.01</v>
       </c>
       <c r="H80" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>0.01</v>
@@ -12251,22 +12251,22 @@
         <v>0.01</v>
       </c>
       <c r="C81" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D81" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E81" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="H81" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0.01</v>
@@ -12280,19 +12280,19 @@
         <v>0.01</v>
       </c>
       <c r="C82" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D82" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E82" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F82" t="n">
         <v>0.04</v>
       </c>
       <c r="G82" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H82" t="n">
         <v>-0.01</v>
@@ -12309,19 +12309,19 @@
         <v>0.02</v>
       </c>
       <c r="C83" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D83" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E83" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F83" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G83" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H83" t="n">
         <v>-0</v>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -12387,13 +12387,13 @@
         <v>1</v>
       </c>
       <c r="B86" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C86" t="n">
         <v>0.03</v>
       </c>
-      <c r="C86" t="n">
-        <v>0.04</v>
-      </c>
       <c r="D86" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E86" t="n">
         <v>0.01</v>
@@ -12402,16 +12402,16 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="87">
@@ -12419,31 +12419,31 @@
         <v>2</v>
       </c>
       <c r="B87" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C87" t="n">
         <v>0.08</v>
       </c>
-      <c r="C87" t="n">
-        <v>0.09</v>
-      </c>
       <c r="D87" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="E87" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F87" t="n">
         <v>-0.01</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="88">
@@ -12451,31 +12451,31 @@
         <v>3</v>
       </c>
       <c r="B88" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C88" t="n">
         <v>0.11</v>
       </c>
-      <c r="C88" t="n">
-        <v>0.13</v>
-      </c>
       <c r="D88" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E88" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F88" t="n">
         <v>-0.02</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="89">
@@ -12483,31 +12483,31 @@
         <v>4</v>
       </c>
       <c r="B89" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C89" t="n">
         <v>0.13</v>
       </c>
-      <c r="C89" t="n">
-        <v>0.15</v>
-      </c>
       <c r="D89" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F89" t="n">
         <v>-0.03</v>
       </c>
       <c r="G89" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="H89" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H89" t="n">
-        <v>-0.22</v>
-      </c>
       <c r="I89" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="90">
@@ -12515,31 +12515,31 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="C90" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="D90" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="E90" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G90" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="H90" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H90" t="n">
-        <v>-0.23</v>
-      </c>
       <c r="I90" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.01</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="93">
@@ -12619,7 +12619,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
         <v>-0.01</v>
@@ -12717,7 +12717,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C99" t="n">
         <v>-0</v>
@@ -12735,7 +12735,7 @@
         <v>-0.01</v>
       </c>
       <c r="H99" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I99" t="n">
         <v>-0.03</v>
@@ -12921,7 +12921,7 @@
         <v>-0.02</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G106" t="n">
         <v>0.02</v>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -13005,7 +13005,7 @@
         <v>-0.01</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="H109" t="n">
         <v>-0.04</v>
@@ -13040,10 +13040,10 @@
         <v>-0.02</v>
       </c>
       <c r="H110" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I110" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="I110" t="n">
-        <v>-0.05</v>
       </c>
       <c r="J110" t="n">
         <v>-0.36</v>
@@ -13104,7 +13104,7 @@
         <v>-0.03</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I112" t="n">
         <v>-0.05</v>
@@ -13127,7 +13127,7 @@
         <v>-0.02</v>
       </c>
       <c r="E113" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F113" t="n">
         <v>-0.01</v>
@@ -13142,7 +13142,7 @@
         <v>-0.05</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.68</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -13239,7 +13239,7 @@
         <v>0.04</v>
       </c>
       <c r="D119" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="E119" t="n">
         <v>0.05</v>
@@ -13320,10 +13320,10 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="C122" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="D122" t="n">
         <v>1.7</v>
@@ -13521,7 +13521,7 @@
         <v>-0.05</v>
       </c>
       <c r="E129" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F129" t="n">
         <v>0.06</v>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -13611,7 +13611,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I132" t="n">
         <v>-0.03</v>
@@ -13643,10 +13643,10 @@
         <v>-0.18</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J133" t="n">
         <v>-0.16</v>
@@ -13657,7 +13657,7 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C134" t="n">
         <v>0.11</v>
@@ -13675,13 +13675,13 @@
         <v>-0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="I134" t="n">
         <v>-0.14</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="135">
@@ -13721,13 +13721,13 @@
         <v>5</v>
       </c>
       <c r="B136" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C136" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="D136" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="E136" t="n">
         <v>0.24</v>
@@ -13742,10 +13742,10 @@
         <v>-0.35</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.8</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="139">
@@ -13813,7 +13813,7 @@
         <v>-0.01</v>
       </c>
       <c r="D141" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E141" t="n">
         <v>-0.03</v>
@@ -13842,7 +13842,7 @@
         <v>-0.04</v>
       </c>
       <c r="D142" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E142" t="n">
         <v>-0.12</v>
@@ -13871,7 +13871,7 @@
         <v>-0.05</v>
       </c>
       <c r="D143" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E143" t="n">
         <v>-0.17</v>
@@ -13883,7 +13883,7 @@
         <v>-0.02</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I143" t="n">
         <v>0.02</v>
@@ -13900,7 +13900,7 @@
         <v>-0.04</v>
       </c>
       <c r="D144" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="E144" t="n">
         <v>-0.18</v>
@@ -13912,7 +13912,7 @@
         <v>-0.02</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I144" t="n">
         <v>0.02</v>
@@ -13923,13 +13923,13 @@
         <v>5</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="D145" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="E145" t="n">
         <v>-0.2</v>
@@ -13941,7 +13941,7 @@
         <v>-0.03</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="I145" t="n">
         <v>-0</v>
@@ -14089,10 +14089,10 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="D151" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E151" t="n">
         <v>-0.07000000000000001</v>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
         <v>-0.02</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D155" t="n">
         <v>-0.07000000000000001</v>
@@ -14214,7 +14214,7 @@
         <v>-0.01</v>
       </c>
       <c r="H155" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I155" t="n">
         <v>-0.03</v>
@@ -14237,22 +14237,22 @@
         <v>-0.08</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F156" t="n">
         <v>-0.05</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I156" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="157">
@@ -14260,7 +14260,7 @@
         <v>3</v>
       </c>
       <c r="B157" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="C157" t="n">
         <v>-0.08</v>
@@ -14269,22 +14269,22 @@
         <v>-0.12</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F157" t="n">
         <v>-0.1</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J157" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="158">
@@ -14292,31 +14292,31 @@
         <v>4</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="D158" t="n">
         <v>-0.14</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="F158" t="n">
         <v>-0.14</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="J158" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -14324,7 +14324,7 @@
         <v>5</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="C159" t="n">
         <v>-0.14</v>
@@ -14333,22 +14333,22 @@
         <v>-0.18</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="F159" t="n">
         <v>-0.17</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="I159" t="n">
         <v>-0.14</v>
       </c>
       <c r="J159" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="162">
@@ -14445,7 +14445,7 @@
         <v>-0.09</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="E165" t="n">
         <v>-0.21</v>
@@ -14474,7 +14474,7 @@
         <v>-0.08</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="E166" t="n">
         <v>-0.23</v>
@@ -14500,10 +14500,10 @@
         <v>-0.01</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="E167" t="n">
         <v>-0.22</v>
@@ -14515,7 +14515,7 @@
         <v>0.05</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="I167" t="n">
         <v>0.25</v>
@@ -14526,16 +14526,16 @@
         <v>5</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="C168" t="n">
         <v>-0.09</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.57</v>
+        <v>-0.59</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="F168" t="n">
         <v>-0</v>
@@ -14544,7 +14544,7 @@
         <v>0.05</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="I168" t="n">
         <v>0.25</v>
@@ -14649,7 +14649,7 @@
         <v>0.01</v>
       </c>
       <c r="H172" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
         <v>-0</v>
@@ -14663,7 +14663,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D173" t="n">
         <v>-0.02</v>
@@ -14689,10 +14689,10 @@
         <v>4</v>
       </c>
       <c r="B174" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D174" t="n">
         <v>-0.02</v>
@@ -14775,7 +14775,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>税収（ＳＮＡベース国・地方対ＧＤＰ比）（％pt）</t>
+          <t>税収（ＳＮＡベース対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>公債等残高（対ＧＤＰ比）（％pt）</t>
+          <t>公債等残高（国・地方対ＧＤＰ比）（％pt）</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
         <v>-0.03</v>
       </c>
       <c r="H178" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I178" t="n">
         <v>-0.04</v>
@@ -14846,13 +14846,13 @@
         <v>-0</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J179" t="n">
         <v>0.44</v>
@@ -14863,7 +14863,7 @@
         <v>3</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="C180" t="n">
         <v>-0.11</v>
@@ -14872,22 +14872,22 @@
         <v>-0.24</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F180" t="n">
         <v>-0.02</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J180" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="181">
@@ -14895,10 +14895,10 @@
         <v>4</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="D181" t="n">
         <v>-0.22</v>
@@ -14910,16 +14910,16 @@
         <v>-0.02</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J181" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="182">
@@ -14927,31 +14927,31 @@
         <v>5</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F182" t="n">
         <v>-0</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="J182" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/multipliers_table_port.xlsx
+++ b/output/multipliers_table_port.xlsx
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="H5" t="n">
         <v>0.39</v>
@@ -614,7 +614,7 @@
         <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -716,7 +716,7 @@
         <v>-0.12</v>
       </c>
       <c r="D11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="E11" t="n">
         <v>0.21</v>
@@ -797,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
         <v>-0.12</v>
@@ -884,10 +884,10 @@
         <v>1.6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="E17" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="F17" t="n">
         <v>-0.16</v>
@@ -902,7 +902,7 @@
         <v>-0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.91</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="18">
@@ -913,7 +913,7 @@
         <v>0.14</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D18" t="n">
         <v>0.3</v>
@@ -934,7 +934,7 @@
         <v>-0.02</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="19">
@@ -966,7 +966,7 @@
         <v>-0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="20">
@@ -998,7 +998,7 @@
         <v>-0.13</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="21">
@@ -1024,13 +1024,13 @@
         <v>-0.08</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="I21" t="n">
         <v>-0.12</v>
       </c>
       <c r="J21" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="24">
@@ -1127,7 +1127,7 @@
         <v>0.12</v>
       </c>
       <c r="D27" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="E27" t="n">
         <v>0.5</v>
@@ -1156,7 +1156,7 @@
         <v>0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E28" t="n">
         <v>0.38</v>
@@ -1328,7 +1328,7 @@
         <v>0.2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H34" t="n">
         <v>-0.05</v>
@@ -1374,7 +1374,7 @@
         <v>0.02</v>
       </c>
       <c r="C36" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="D36" t="n">
         <v>0.85</v>
@@ -1487,10 +1487,10 @@
         <v>1.6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="E40" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="F40" t="n">
         <v>-0.16</v>
@@ -1505,7 +1505,7 @@
         <v>-0.7</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.91</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="41">
@@ -1537,7 +1537,7 @@
         <v>-0.7</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.58</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="42">
@@ -1560,7 +1560,7 @@
         <v>-0.39</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H42" t="n">
         <v>-0.76</v>
@@ -1569,7 +1569,7 @@
         <v>-0.77</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.87</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="43">
@@ -1598,10 +1598,10 @@
         <v>-0.92</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="J43" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="44">
@@ -1633,7 +1633,7 @@
         <v>-0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="47">
@@ -1730,7 +1730,7 @@
         <v>-0.18</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.63</v>
+        <v>-1.65</v>
       </c>
       <c r="E50" t="n">
         <v>-0.17</v>
@@ -1745,7 +1745,7 @@
         <v>-0.24</v>
       </c>
       <c r="I50" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="51">
@@ -1753,13 +1753,13 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="C51" t="n">
         <v>-0.22</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.02</v>
+        <v>-2.05</v>
       </c>
       <c r="E51" t="n">
         <v>-0.21</v>
@@ -1774,7 +1774,7 @@
         <v>-0.4</v>
       </c>
       <c r="I51" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="52">
@@ -1782,13 +1782,13 @@
         <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="C52" t="n">
         <v>-0.23</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.24</v>
+        <v>-2.28</v>
       </c>
       <c r="E52" t="n">
         <v>-0.24</v>
@@ -1800,10 +1800,10 @@
         <v>0.03</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="I52" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="53">
@@ -1817,7 +1817,7 @@
         <v>-0.24</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.37</v>
+        <v>-2.41</v>
       </c>
       <c r="E53" t="n">
         <v>-0.27</v>
@@ -1829,10 +1829,10 @@
         <v>0.05</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="I53" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="55">
@@ -1931,7 +1931,7 @@
         <v>-0.05</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H57" t="n">
         <v>0.02</v>
@@ -1960,7 +1960,7 @@
         <v>-0.1</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="H58" t="n">
         <v>0.02</v>
@@ -1977,7 +1977,7 @@
         <v>-0.11</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="D59" t="n">
         <v>-0.27</v>
@@ -1989,7 +1989,7 @@
         <v>-0.15</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="H59" t="n">
         <v>0.02</v>
@@ -2003,16 +2003,16 @@
         <v>5</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="D60" t="n">
         <v>-0.34</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="F60" t="n">
         <v>-0.2</v>
@@ -2108,7 +2108,7 @@
         <v>0.97</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.59</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="64">
@@ -2119,7 +2119,7 @@
         <v>-0.45</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.53</v>
+        <v>-0.54</v>
       </c>
       <c r="D64" t="n">
         <v>-0.3</v>
@@ -2140,7 +2140,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.27</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="65">
@@ -2148,16 +2148,16 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.47</v>
+        <v>-0.46</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="F65" t="n">
         <v>0.14</v>
@@ -2169,10 +2169,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.04</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="66">
@@ -2180,31 +2180,31 @@
         <v>4</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.68</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.63</v>
+        <v>-0.65</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.61</v>
+        <v>-0.6</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="F66" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="G66" t="n">
         <v>1.01</v>
       </c>
       <c r="H66" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.9</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="67">
@@ -2212,31 +2212,31 @@
         <v>5</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.59</v>
+        <v>-0.61</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="F67" t="n">
         <v>0.27</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H67" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.86</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="70">
@@ -2333,7 +2333,7 @@
         <v>-1.02</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="E73" t="n">
         <v>-2.22</v>
@@ -2348,7 +2348,7 @@
         <v>-0.5</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="74">
@@ -2362,7 +2362,7 @@
         <v>-0.95</v>
       </c>
       <c r="D74" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="E74" t="n">
         <v>-2.16</v>
@@ -2374,7 +2374,7 @@
         <v>0.04</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="I74" t="n">
         <v>0.09</v>
@@ -2391,10 +2391,10 @@
         <v>-0.93</v>
       </c>
       <c r="D75" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.1</v>
+        <v>-2.09</v>
       </c>
       <c r="F75" t="n">
         <v>-0</v>
@@ -2406,7 +2406,7 @@
         <v>-0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="76">
@@ -2420,7 +2420,7 @@
         <v>-1.05</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="E76" t="n">
         <v>-2.12</v>
@@ -2432,7 +2432,7 @@
         <v>0.08</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.03</v>
+        <v>-1.04</v>
       </c>
       <c r="I76" t="n">
         <v>0.18</v>
@@ -2534,7 +2534,7 @@
         <v>-0.11</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H80" t="n">
         <v>0.03</v>
@@ -2563,7 +2563,7 @@
         <v>-0.19</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="H81" t="n">
         <v>0.02</v>
@@ -2711,7 +2711,7 @@
         <v>0.75</v>
       </c>
       <c r="J86" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="87">
@@ -2722,7 +2722,7 @@
         <v>-0.76</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.86</v>
+        <v>-0.87</v>
       </c>
       <c r="D87" t="n">
         <v>-2.5</v>
@@ -2743,7 +2743,7 @@
         <v>0.7</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2757,10 +2757,10 @@
         <v>-0.72</v>
       </c>
       <c r="D88" t="n">
-        <v>-2.61</v>
+        <v>-2.6</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="F88" t="n">
         <v>0.22</v>
@@ -2775,7 +2775,7 @@
         <v>0.73</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.12</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="89">
@@ -2786,10 +2786,10 @@
         <v>-0.68</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="D89" t="n">
-        <v>-2.68</v>
+        <v>-2.67</v>
       </c>
       <c r="E89" t="n">
         <v>-0.59</v>
@@ -2807,7 +2807,7 @@
         <v>0.77</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.12</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="90">
@@ -2818,10 +2818,10 @@
         <v>-0.72</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="D90" t="n">
-        <v>-2.8</v>
+        <v>-2.79</v>
       </c>
       <c r="E90" t="n">
         <v>-0.58</v>
@@ -2839,7 +2839,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.06</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="93">
@@ -3023,7 +3023,7 @@
         <v>-0.37</v>
       </c>
       <c r="D99" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E99" t="n">
         <v>-0.79</v>
@@ -3314,7 +3314,7 @@
         <v>0.32</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="110">
@@ -3346,7 +3346,7 @@
         <v>0.32</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.15</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="111">
@@ -3378,7 +3378,7 @@
         <v>0.32</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.51</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="112">
@@ -3386,7 +3386,7 @@
         <v>4</v>
       </c>
       <c r="B112" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="C112" t="n">
         <v>-0.22</v>
@@ -3410,7 +3410,7 @@
         <v>0.33</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.87</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="113">
@@ -3442,7 +3442,7 @@
         <v>0.34</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.21</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="116">
@@ -3626,7 +3626,7 @@
         <v>2.69</v>
       </c>
       <c r="D122" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="E122" t="n">
         <v>4.17</v>
@@ -3641,7 +3641,7 @@
         <v>-1.85</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="124">
@@ -3949,7 +3949,7 @@
         <v>0.2</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.23</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="134">
@@ -4013,7 +4013,7 @@
         <v>0.57</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.15</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="136">
@@ -4045,7 +4045,7 @@
         <v>0.83</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.84</v>
+        <v>-8.59</v>
       </c>
     </row>
     <row r="139">
@@ -4154,10 +4154,10 @@
         <v>-0.19</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="I142" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="143">
@@ -4165,7 +4165,7 @@
         <v>3</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="C143" t="n">
         <v>-0.35</v>
@@ -4343,7 +4343,7 @@
         <v>-0.02</v>
       </c>
       <c r="G149" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H149" t="n">
         <v>0.02</v>
@@ -4415,7 +4415,7 @@
         <v>5</v>
       </c>
       <c r="B152" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="C152" t="n">
         <v>-0.23</v>
@@ -4520,7 +4520,7 @@
         <v>-0.28</v>
       </c>
       <c r="J155" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -4552,7 +4552,7 @@
         <v>-0.32</v>
       </c>
       <c r="J156" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="157">
@@ -4584,7 +4584,7 @@
         <v>-0.37</v>
       </c>
       <c r="J157" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="158">
@@ -4607,7 +4607,7 @@
         <v>-0.71</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="H158" t="n">
         <v>-0.41</v>
@@ -4616,7 +4616,7 @@
         <v>-0.38</v>
       </c>
       <c r="J158" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="159">
@@ -4639,16 +4639,16 @@
         <v>-0.74</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="J159" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="162">
@@ -4748,7 +4748,7 @@
         <v>-2.23</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.53</v>
+        <v>-0.54</v>
       </c>
       <c r="F165" t="n">
         <v>-0</v>
@@ -4832,10 +4832,10 @@
         <v>0.46</v>
       </c>
       <c r="D168" t="n">
-        <v>-3.69</v>
+        <v>-3.7</v>
       </c>
       <c r="E168" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F168" t="n">
         <v>-0</v>
@@ -4847,7 +4847,7 @@
         <v>-0.39</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="170">
@@ -5033,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>-0.23</v>
       </c>
       <c r="J179" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="180">
@@ -5187,7 +5187,7 @@
         <v>-0.27</v>
       </c>
       <c r="J180" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="181">
@@ -5219,7 +5219,7 @@
         <v>-0.27</v>
       </c>
       <c r="J181" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="182">
@@ -5233,7 +5233,7 @@
         <v>-1.31</v>
       </c>
       <c r="D182" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="E182" t="n">
         <v>-0.65</v>
@@ -5251,7 +5251,7 @@
         <v>-0.24</v>
       </c>
       <c r="J182" t="n">
-        <v>4.96</v>
+        <v>5.06</v>
       </c>
     </row>
   </sheetData>
@@ -10262,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>-0.04</v>
@@ -10314,7 +10314,7 @@
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -10416,7 +10416,7 @@
         <v>-0.02</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
         <v>-0.01</v>
@@ -10497,7 +10497,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
         <v>0.02</v>
@@ -10584,10 +10584,10 @@
         <v>-0.03</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="F17" t="n">
         <v>-0.02</v>
@@ -10602,7 +10602,7 @@
         <v>0.04</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
@@ -10613,7 +10613,7 @@
         <v>-0.02</v>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="D18" t="n">
         <v>-0.04</v>
@@ -10634,7 +10634,7 @@
         <v>-0.06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="19">
@@ -10666,7 +10666,7 @@
         <v>-0.04</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="20">
@@ -10698,7 +10698,7 @@
         <v>-0.05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="21">
@@ -10724,13 +10724,13 @@
         <v>-0.04</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="I21" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="24">
@@ -10827,7 +10827,7 @@
         <v>-0.04</v>
       </c>
       <c r="D27" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E27" t="n">
         <v>-0.07000000000000001</v>
@@ -10856,7 +10856,7 @@
         <v>-0.03</v>
       </c>
       <c r="D28" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="E28" t="n">
         <v>-0.08</v>
@@ -11028,7 +11028,7 @@
         <v>0.01</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H34" t="n">
         <v>0.01</v>
@@ -11074,7 +11074,7 @@
         <v>-0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D36" t="n">
         <v>0.03</v>
@@ -11187,10 +11187,10 @@
         <v>-0.03</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E40" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="F40" t="n">
         <v>-0.02</v>
@@ -11205,7 +11205,7 @@
         <v>0.04</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
@@ -11237,7 +11237,7 @@
         <v>0.01</v>
       </c>
       <c r="J41" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
@@ -11260,7 +11260,7 @@
         <v>0.01</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0.01</v>
@@ -11269,7 +11269,7 @@
         <v>0.01</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43">
@@ -11298,10 +11298,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J43" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="44">
@@ -11333,7 +11333,7 @@
         <v>0.01</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="47">
@@ -11430,7 +11430,7 @@
         <v>0.02</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="E50" t="n">
         <v>0.02</v>
@@ -11445,7 +11445,7 @@
         <v>0.03</v>
       </c>
       <c r="I50" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="51">
@@ -11453,13 +11453,13 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C51" t="n">
         <v>0.03</v>
       </c>
       <c r="D51" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0.04</v>
@@ -11468,13 +11468,13 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H51" t="n">
         <v>0.09</v>
       </c>
       <c r="I51" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="52">
@@ -11482,13 +11482,13 @@
         <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C52" t="n">
         <v>0.05</v>
       </c>
       <c r="D52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E52" t="n">
         <v>0.04</v>
@@ -11500,10 +11500,10 @@
         <v>-0.01</v>
       </c>
       <c r="H52" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="53">
@@ -11517,7 +11517,7 @@
         <v>0.05</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E53" t="n">
         <v>0.03</v>
@@ -11529,10 +11529,10 @@
         <v>-0.01</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="55">
@@ -11631,7 +11631,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H57" t="n">
         <v>-0</v>
@@ -11660,7 +11660,7 @@
         <v>0.01</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H58" t="n">
         <v>-0</v>
@@ -11677,7 +11677,7 @@
         <v>0.01</v>
       </c>
       <c r="C59" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D59" t="n">
         <v>0.04</v>
@@ -11689,7 +11689,7 @@
         <v>0.02</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H59" t="n">
         <v>-0</v>
@@ -11703,22 +11703,22 @@
         <v>5</v>
       </c>
       <c r="B60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D60" t="n">
         <v>0.05</v>
       </c>
       <c r="E60" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
         <v>0.03</v>
       </c>
       <c r="G60" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -11808,7 +11808,7 @@
         <v>-0.02</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="64">
@@ -11819,7 +11819,7 @@
         <v>0.05</v>
       </c>
       <c r="C64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D64" t="n">
         <v>0.03</v>
@@ -11840,7 +11840,7 @@
         <v>-0.05</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.32</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="65">
@@ -11848,16 +11848,16 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.04</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.05</v>
       </c>
       <c r="F65" t="n">
         <v>-0.01</v>
@@ -11869,10 +11869,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.96</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="66">
@@ -11880,31 +11880,31 @@
         <v>4</v>
       </c>
       <c r="B66" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C66" t="n">
         <v>0.1</v>
       </c>
-      <c r="C66" t="n">
-        <v>0.12</v>
-      </c>
       <c r="D66" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E66" t="n">
         <v>0.06</v>
       </c>
-      <c r="E66" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="F66" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G66" t="n">
         <v>-0.06</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.6</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="67">
@@ -11912,31 +11912,31 @@
         <v>5</v>
       </c>
       <c r="B67" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C67" t="n">
         <v>0.12</v>
       </c>
-      <c r="C67" t="n">
-        <v>0.14</v>
-      </c>
       <c r="D67" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E67" t="n">
         <v>0.08</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.09</v>
       </c>
       <c r="F67" t="n">
         <v>-0.03</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.24</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="70">
@@ -12033,7 +12033,7 @@
         <v>0.08</v>
       </c>
       <c r="D73" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E73" t="n">
         <v>0.16</v>
@@ -12048,7 +12048,7 @@
         <v>0.05</v>
       </c>
       <c r="I73" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="74">
@@ -12062,7 +12062,7 @@
         <v>0.1</v>
       </c>
       <c r="D74" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="E74" t="n">
         <v>0.19</v>
@@ -12074,7 +12074,7 @@
         <v>-0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I74" t="n">
         <v>-0.03</v>
@@ -12091,10 +12091,10 @@
         <v>0.11</v>
       </c>
       <c r="D75" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="E75" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F75" t="n">
         <v>-0</v>
@@ -12106,7 +12106,7 @@
         <v>0.19</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="76">
@@ -12120,7 +12120,7 @@
         <v>0.12</v>
       </c>
       <c r="D76" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="E76" t="n">
         <v>0.21</v>
@@ -12132,7 +12132,7 @@
         <v>-0.02</v>
       </c>
       <c r="H76" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I76" t="n">
         <v>-0.09</v>
@@ -12234,7 +12234,7 @@
         <v>-0</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -12263,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -12327,7 +12327,7 @@
         <v>-0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="85">
@@ -12411,7 +12411,7 @@
         <v>-0.1</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.21</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="87">
@@ -12422,7 +12422,7 @@
         <v>0.06</v>
       </c>
       <c r="C87" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D87" t="n">
         <v>0.16</v>
@@ -12443,7 +12443,7 @@
         <v>-0.16</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.43</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="88">
@@ -12457,10 +12457,10 @@
         <v>0.11</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="E88" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F88" t="n">
         <v>-0.02</v>
@@ -12475,7 +12475,7 @@
         <v>-0.19</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.65</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="89">
@@ -12486,10 +12486,10 @@
         <v>0.11</v>
       </c>
       <c r="C89" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D89" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="E89" t="n">
         <v>0.08</v>
@@ -12507,7 +12507,7 @@
         <v>-0.2</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.86</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="90">
@@ -12518,10 +12518,10 @@
         <v>0.12</v>
       </c>
       <c r="C90" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D90" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E90" t="n">
         <v>0.09</v>
@@ -12539,7 +12539,7 @@
         <v>-0.19</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.09</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="93">
@@ -12723,7 +12723,7 @@
         <v>-0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E99" t="n">
         <v>-0.02</v>
@@ -13014,7 +13014,7 @@
         <v>-0.04</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="110">
@@ -13046,7 +13046,7 @@
         <v>-0.04</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="111">
@@ -13078,7 +13078,7 @@
         <v>-0.05</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="112">
@@ -13086,7 +13086,7 @@
         <v>4</v>
       </c>
       <c r="B112" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C112" t="n">
         <v>0.05</v>
@@ -13110,7 +13110,7 @@
         <v>-0.05</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -13142,7 +13142,7 @@
         <v>-0.05</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="116">
@@ -13326,7 +13326,7 @@
         <v>0.29</v>
       </c>
       <c r="D122" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="E122" t="n">
         <v>0.5600000000000001</v>
@@ -13341,7 +13341,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -13649,7 +13649,7 @@
         <v>-0.08</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="134">
@@ -13713,7 +13713,7 @@
         <v>-0.16</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.04</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="136">
@@ -13745,7 +13745,7 @@
         <v>-0.15</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.81</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="139">
@@ -13854,10 +13854,10 @@
         <v>-0.05</v>
       </c>
       <c r="H142" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="143">
@@ -13865,7 +13865,7 @@
         <v>3</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="C143" t="n">
         <v>-0.05</v>
@@ -14043,7 +14043,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H149" t="n">
         <v>0.01</v>
@@ -14115,7 +14115,7 @@
         <v>5</v>
       </c>
       <c r="B152" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
         <v>-0.11</v>
@@ -14220,7 +14220,7 @@
         <v>-0.03</v>
       </c>
       <c r="J155" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="156">
@@ -14252,7 +14252,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="157">
@@ -14284,7 +14284,7 @@
         <v>-0.11</v>
       </c>
       <c r="J157" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="158">
@@ -14307,7 +14307,7 @@
         <v>-0.14</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H158" t="n">
         <v>-0.12</v>
@@ -14316,7 +14316,7 @@
         <v>-0.12</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="159">
@@ -14339,16 +14339,16 @@
         <v>-0.17</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="J159" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="162">
@@ -14448,7 +14448,7 @@
         <v>-0.28</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="F165" t="n">
         <v>-0</v>
@@ -14532,10 +14532,10 @@
         <v>-0.09</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="F168" t="n">
         <v>-0</v>
@@ -14547,7 +14547,7 @@
         <v>-0.06</v>
       </c>
       <c r="I168" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="170">
@@ -14733,7 +14733,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="180">
@@ -14887,7 +14887,7 @@
         <v>-0.08</v>
       </c>
       <c r="J180" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="181">
@@ -14919,7 +14919,7 @@
         <v>-0.08</v>
       </c>
       <c r="J181" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="182">
@@ -14933,7 +14933,7 @@
         <v>-0.13</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="E182" t="n">
         <v>-0.04</v>
@@ -14951,7 +14951,7 @@
         <v>-0.06</v>
       </c>
       <c r="J182" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/multipliers_table_port.xlsx
+++ b/output/multipliers_table_port.xlsx
@@ -489,25 +489,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="C3" t="n">
         <v>0.21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F3" t="n">
-        <v>3.93</v>
+        <v>4.34</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="I3" t="n">
         <v>0.03</v>
@@ -518,16 +518,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="D4" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>-0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="I4" t="n">
         <v>0.04</v>
@@ -553,10 +553,10 @@
         <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.29</v>
+        <v>-0.23</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -565,10 +565,10 @@
         <v>-0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="6">
@@ -579,13 +579,13 @@
         <v>-0.19</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.34</v>
+        <v>-0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="F6" t="n">
         <v>-0</v>
@@ -594,7 +594,7 @@
         <v>-0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="I6" t="n">
         <v>-0.1</v>
@@ -605,16 +605,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="C7" t="n">
         <v>0.02</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -623,7 +623,7 @@
         <v>-0.03</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I7" t="n">
         <v>-0.08</v>
@@ -684,13 +684,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="D10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="E10" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F10" t="n">
         <v>0.05</v>
@@ -699,7 +699,7 @@
         <v>0.05</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>0.07000000000000001</v>
@@ -713,10 +713,10 @@
         <v>0.01</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="D11" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="E11" t="n">
         <v>0.21</v>
@@ -725,7 +725,7 @@
         <v>0.15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H11" t="n">
         <v>0.01</v>
@@ -745,7 +745,7 @@
         <v>-0.22</v>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="D13" t="n">
         <v>0.17</v>
@@ -783,13 +783,13 @@
         <v>0.11</v>
       </c>
       <c r="G13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H13" t="n">
         <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="14">
@@ -800,19 +800,19 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
         <v>0.08</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H14" t="n">
         <v>0.01</v>
@@ -881,28 +881,28 @@
         <v>1.3</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="D17" t="n">
         <v>0.66</v>
       </c>
       <c r="E17" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="F17" t="n">
         <v>-0.16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7</v>
+        <v>-0.75</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.87</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="18">
@@ -910,13 +910,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E18" t="n">
         <v>0.43</v>
@@ -925,16 +925,16 @@
         <v>-0.1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="19">
@@ -942,31 +942,31 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E19" t="n">
         <v>0.21</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.15</v>
+        <v>-0.09</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="J19" t="n">
-        <v>0.79</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="20">
@@ -977,28 +977,28 @@
         <v>-0.02</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="E20" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="J20" t="n">
-        <v>1.05</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="21">
@@ -1006,31 +1006,31 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="D21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.22</v>
+        <v>-0.13</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="J21" t="n">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="24">
@@ -1092,25 +1092,25 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="C26" t="n">
         <v>0.21</v>
       </c>
       <c r="D26" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="E26" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F26" t="n">
-        <v>3.93</v>
+        <v>4.34</v>
       </c>
       <c r="G26" t="n">
         <v>-0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="I26" t="n">
         <v>0.03</v>
@@ -1121,28 +1121,28 @@
         <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="C27" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="F27" t="n">
-        <v>3.93</v>
+        <v>4.4</v>
       </c>
       <c r="G27" t="n">
         <v>-0.01</v>
       </c>
       <c r="H27" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1150,28 +1150,28 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D28" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F28" t="n">
-        <v>3.93</v>
+        <v>4.45</v>
       </c>
       <c r="G28" t="n">
         <v>-0.06</v>
       </c>
       <c r="H28" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="29">
@@ -1179,28 +1179,28 @@
         <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.33</v>
+        <v>-0.19</v>
       </c>
       <c r="E29" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="F29" t="n">
-        <v>3.93</v>
+        <v>4.5</v>
       </c>
       <c r="G29" t="n">
         <v>-0.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="30">
@@ -1208,25 +1208,25 @@
         <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.75</v>
+        <v>-0.48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="F30" t="n">
-        <v>3.93</v>
+        <v>4.55</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="H30" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="I30" t="n">
         <v>-0.3</v>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="D33" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="E33" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F33" t="n">
         <v>0.05</v>
@@ -1302,7 +1302,7 @@
         <v>0.05</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>0.07000000000000001</v>
@@ -1316,10 +1316,10 @@
         <v>0.01</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="D34" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="E34" t="n">
         <v>0.37</v>
@@ -1328,10 +1328,10 @@
         <v>0.2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="I34" t="n">
         <v>0.06</v>
@@ -1345,19 +1345,19 @@
         <v>0.01</v>
       </c>
       <c r="C35" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="E35" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="F35" t="n">
         <v>0.34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H35" t="n">
         <v>-0.04</v>
@@ -1374,22 +1374,22 @@
         <v>0.02</v>
       </c>
       <c r="C36" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="D36" t="n">
         <v>0.85</v>
       </c>
       <c r="E36" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F36" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G36" t="n">
         <v>0.47</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I36" t="n">
         <v>0.03</v>
@@ -1403,25 +1403,25 @@
         <v>0.01</v>
       </c>
       <c r="C37" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="D37" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="E37" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="F37" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="G37" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="39">
@@ -1484,28 +1484,28 @@
         <v>1.3</v>
       </c>
       <c r="C40" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="D40" t="n">
         <v>0.66</v>
       </c>
       <c r="E40" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="F40" t="n">
         <v>-0.16</v>
       </c>
       <c r="G40" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7</v>
+        <v>-0.75</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.87</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="41">
@@ -1513,31 +1513,31 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="C41" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="D41" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="G41" t="n">
         <v>0.1</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.51</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="42">
@@ -1545,31 +1545,31 @@
         <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="C42" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="D42" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="E42" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
       <c r="G42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.76</v>
+        <v>-0.79</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.77</v>
+        <v>-0.83</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.77</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="43">
@@ -1577,31 +1577,31 @@
         <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="C43" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="D43" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="E43" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.84</v>
+        <v>-0.89</v>
       </c>
       <c r="J43" t="n">
-        <v>0.19</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="44">
@@ -1609,31 +1609,31 @@
         <v>5</v>
       </c>
       <c r="B44" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="C44" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="D44" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="E44" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.67</v>
+        <v>-0.62</v>
       </c>
       <c r="G44" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.07</v>
+        <v>-1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.9</v>
+        <v>-0.93</v>
       </c>
       <c r="J44" t="n">
-        <v>1.25</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="47">
@@ -1701,19 +1701,19 @@
         <v>-0.11</v>
       </c>
       <c r="D49" t="n">
-        <v>-1</v>
+        <v>-0.88</v>
       </c>
       <c r="E49" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
         <v>-0.1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0.09</v>
       </c>
       <c r="I49" t="n">
         <v>-0.01</v>
@@ -1730,10 +1730,10 @@
         <v>-0.18</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.65</v>
+        <v>-1.46</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1742,10 +1742,10 @@
         <v>0.01</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="51">
@@ -1753,16 +1753,16 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.05</v>
+        <v>-1.83</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0.02</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="I51" t="n">
         <v>0.04</v>
@@ -1782,16 +1782,16 @@
         <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.28</v>
+        <v>-2.08</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.24</v>
+        <v>-0.31</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0.03</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.57</v>
+        <v>-0.67</v>
       </c>
       <c r="I52" t="n">
         <v>0.08</v>
@@ -1811,16 +1811,16 @@
         <v>5</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.41</v>
+        <v>-2.25</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.27</v>
+        <v>-0.36</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0.05</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.71</v>
+        <v>-0.87</v>
       </c>
       <c r="I53" t="n">
         <v>0.12</v>
@@ -1890,7 +1890,7 @@
         <v>-0.01</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="D56" t="n">
         <v>-0.03</v>
@@ -1931,7 +1931,7 @@
         <v>-0.05</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="H57" t="n">
         <v>0.02</v>
@@ -1948,13 +1948,13 @@
         <v>-0.06</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="F58" t="n">
         <v>-0.1</v>
@@ -1977,16 +1977,16 @@
         <v>-0.11</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="G59" t="n">
         <v>-0.18</v>
@@ -2006,25 +2006,25 @@
         <v>-0.18</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.24</v>
+        <v>-0.29</v>
       </c>
       <c r="D60" t="n">
         <v>-0.34</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="G60" t="n">
         <v>-0.24</v>
       </c>
       <c r="H60" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="62">
@@ -2084,10 +2084,10 @@
         <v>1</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="D63" t="n">
         <v>-0.14</v>
@@ -2099,16 +2099,16 @@
         <v>0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="H63" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.37</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="64">
@@ -2119,28 +2119,28 @@
         <v>-0.45</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="E64" t="n">
         <v>-0.28</v>
       </c>
       <c r="F64" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="H64" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.84</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="65">
@@ -2151,28 +2151,28 @@
         <v>-0.6</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
       <c r="D65" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E65" t="n">
         <v>-0.46</v>
       </c>
-      <c r="E65" t="n">
-        <v>-0.45</v>
-      </c>
       <c r="F65" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="G65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H65" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="I65" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.43</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="66">
@@ -2180,31 +2180,31 @@
         <v>4</v>
       </c>
       <c r="B66" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="C66" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>-0.65</v>
       </c>
-      <c r="D66" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="E66" t="n">
-        <v>-0.57</v>
+        <v>-0.59</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H66" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="I66" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.11</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="67">
@@ -2212,31 +2212,31 @@
         <v>5</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.75</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.61</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.73</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.66</v>
+        <v>-0.71</v>
       </c>
       <c r="F67" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H67" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="I67" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.88</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="70">
@@ -2298,25 +2298,25 @@
         <v>1</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="C72" t="n">
         <v>-1.08</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.21</v>
+        <v>-2.18</v>
       </c>
       <c r="F72" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="I72" t="n">
         <v>-0.02</v>
@@ -2327,25 +2327,25 @@
         <v>2</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.02</v>
+        <v>-1.04</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="E73" t="n">
         <v>-2.22</v>
       </c>
       <c r="F73" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0.01</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.5</v>
+        <v>-0.59</v>
       </c>
       <c r="I73" t="n">
         <v>-0.02</v>
@@ -2356,25 +2356,25 @@
         <v>3</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.37</v>
+        <v>-0.43</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="E74" t="n">
-        <v>-2.16</v>
+        <v>-2.18</v>
       </c>
       <c r="F74" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0.04</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.71</v>
+        <v>-0.85</v>
       </c>
       <c r="I74" t="n">
         <v>0.09</v>
@@ -2385,28 +2385,28 @@
         <v>4</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.25</v>
+        <v>-0.34</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.93</v>
+        <v>-0.99</v>
       </c>
       <c r="D75" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.09</v>
+        <v>-2.15</v>
       </c>
       <c r="F75" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0.06</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.87</v>
+        <v>-1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="76">
@@ -2414,16 +2414,16 @@
         <v>5</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.05</v>
+        <v>-1.12</v>
       </c>
       <c r="D76" t="n">
-        <v>0.92</v>
+        <v>0.38</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.12</v>
+        <v>-2.2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2432,10 +2432,10 @@
         <v>0.08</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.04</v>
+        <v>-1.32</v>
       </c>
       <c r="I76" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="78">
@@ -2493,10 +2493,10 @@
         <v>-0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="E79" t="n">
         <v>-0.09</v>
@@ -2522,16 +2522,16 @@
         <v>-0</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="D80" t="n">
         <v>-0.24</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="G80" t="n">
         <v>-0.07000000000000001</v>
@@ -2548,28 +2548,28 @@
         <v>3</v>
       </c>
       <c r="B81" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.37</v>
+        <v>-0.43</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="H81" t="n">
         <v>0.02</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="82">
@@ -2577,28 +2577,28 @@
         <v>4</v>
       </c>
       <c r="B82" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="C82" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="F82" t="n">
         <v>-0.26</v>
       </c>
-      <c r="D82" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="G82" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="H82" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="83">
@@ -2606,28 +2606,28 @@
         <v>5</v>
       </c>
       <c r="B83" t="n">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.5</v>
+        <v>-0.54</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.41</v>
+        <v>-0.46</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="H83" t="n">
         <v>0.01</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="85">
@@ -2690,28 +2690,28 @@
         <v>-0.72</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="D86" t="n">
-        <v>-2.33</v>
+        <v>-2.32</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="F86" t="n">
         <v>0.09</v>
       </c>
       <c r="G86" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H86" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="J86" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="87">
@@ -2719,31 +2719,31 @@
         <v>2</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.76</v>
+        <v>-0.79</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.87</v>
+        <v>-0.9</v>
       </c>
       <c r="D87" t="n">
-        <v>-2.5</v>
+        <v>-2.51</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F87" t="n">
         <v>0.15</v>
       </c>
       <c r="G87" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H87" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="88">
@@ -2751,31 +2751,31 @@
         <v>3</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.72</v>
+        <v>-0.79</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.72</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D88" t="n">
-        <v>-2.6</v>
+        <v>-2.65</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.63</v>
+        <v>-0.68</v>
       </c>
       <c r="F88" t="n">
         <v>0.22</v>
       </c>
       <c r="G88" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="H88" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.85</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="89">
@@ -2783,31 +2783,31 @@
         <v>4</v>
       </c>
       <c r="B89" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="E89" t="n">
         <v>-0.68</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-0.59</v>
       </c>
       <c r="F89" t="n">
         <v>0.3</v>
       </c>
       <c r="G89" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.83</v>
+        <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.75</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="90">
@@ -2815,31 +2815,31 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.72</v>
+        <v>-0.86</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.55</v>
+        <v>-0.71</v>
       </c>
       <c r="D90" t="n">
-        <v>-2.79</v>
+        <v>-2.92</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.58</v>
+        <v>-0.7</v>
       </c>
       <c r="F90" t="n">
         <v>0.39</v>
       </c>
       <c r="G90" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.55</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="93">
@@ -2904,10 +2904,10 @@
         <v>-0.25</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E95" t="n">
         <v>-0.82</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="I95" t="n">
         <v>-0.01</v>
@@ -2930,16 +2930,16 @@
         <v>2</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2948,10 +2948,10 @@
         <v>0.01</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="I96" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="97">
@@ -2959,16 +2959,16 @@
         <v>3</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2977,10 +2977,10 @@
         <v>0.02</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="98">
@@ -2988,16 +2988,16 @@
         <v>4</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="D98" t="n">
-        <v>-0</v>
+        <v>-0.16</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0.02</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.32</v>
+        <v>-0.42</v>
       </c>
       <c r="I98" t="n">
         <v>0.05</v>
@@ -3017,16 +3017,16 @@
         <v>5</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="D99" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.79</v>
+        <v>-0.82</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0.03</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.4</v>
+        <v>-0.52</v>
       </c>
       <c r="I99" t="n">
         <v>0.07000000000000001</v>
@@ -3096,7 +3096,7 @@
         <v>-0</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="D102" t="n">
         <v>0.46</v>
@@ -3111,7 +3111,7 @@
         <v>-0.01</v>
       </c>
       <c r="H102" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I102" t="n">
         <v>-0.02</v>
@@ -3125,19 +3125,19 @@
         <v>-0</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="D103" t="n">
         <v>0.41</v>
       </c>
       <c r="E103" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H103" t="n">
         <v>0.01</v>
@@ -3154,13 +3154,13 @@
         <v>-0.01</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="D104" t="n">
         <v>0.37</v>
       </c>
       <c r="E104" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="F104" t="n">
         <v>-0.07000000000000001</v>
@@ -3183,16 +3183,16 @@
         <v>-0.01</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="D105" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="G105" t="n">
         <v>-0.11</v>
@@ -3209,22 +3209,22 @@
         <v>5</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="D106" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="E106" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="H106" t="n">
         <v>0.01</v>
@@ -3290,31 +3290,31 @@
         <v>1</v>
       </c>
       <c r="B109" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="C109" t="n">
         <v>-0.35</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="F109" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G109" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H109" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="I109" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.75</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="110">
@@ -3322,31 +3322,31 @@
         <v>2</v>
       </c>
       <c r="B110" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="F110" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G110" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="I110" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.14</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="111">
@@ -3354,31 +3354,31 @@
         <v>3</v>
       </c>
       <c r="B111" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.24</v>
+        <v>-0.29</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="F111" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G111" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H111" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="I111" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.49</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="112">
@@ -3386,31 +3386,31 @@
         <v>4</v>
       </c>
       <c r="B112" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.22</v>
+        <v>-0.29</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.23</v>
+        <v>-0.28</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G112" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H112" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.84</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="113">
@@ -3418,31 +3418,31 @@
         <v>5</v>
       </c>
       <c r="B113" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.24</v>
+        <v>-0.31</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="F113" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G113" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H113" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I113" t="n">
         <v>0.38</v>
       </c>
-      <c r="I113" t="n">
-        <v>0.34</v>
-      </c>
       <c r="J113" t="n">
-        <v>-2.16</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="116">
@@ -3504,16 +3504,16 @@
         <v>1</v>
       </c>
       <c r="B118" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="C118" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="D118" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="E118" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.2</v>
+        <v>-0.23</v>
       </c>
       <c r="I118" t="n">
         <v>-0.02</v>
@@ -3533,16 +3533,16 @@
         <v>2</v>
       </c>
       <c r="B119" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="C119" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="D119" t="n">
-        <v>4.16</v>
+        <v>3.65</v>
       </c>
       <c r="E119" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>0.01</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.53</v>
+        <v>-0.61</v>
       </c>
       <c r="I119" t="n">
         <v>-0.01</v>
@@ -3562,16 +3562,16 @@
         <v>3</v>
       </c>
       <c r="B120" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="C120" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="D120" t="n">
-        <v>7.32</v>
+        <v>6.36</v>
       </c>
       <c r="E120" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>0.03</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.93</v>
+        <v>-1.08</v>
       </c>
       <c r="I120" t="n">
         <v>-0.01</v>
@@ -3591,16 +3591,16 @@
         <v>4</v>
       </c>
       <c r="B121" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="C121" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="D121" t="n">
-        <v>10.98</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E121" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3609,10 +3609,10 @@
         <v>0.05</v>
       </c>
       <c r="H121" t="n">
-        <v>-1.38</v>
+        <v>-1.61</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="122">
@@ -3620,16 +3620,16 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="C122" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="D122" t="n">
-        <v>15.11</v>
+        <v>13.14</v>
       </c>
       <c r="E122" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3638,10 +3638,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-1.85</v>
+        <v>-2.15</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="124">
@@ -3699,10 +3699,10 @@
         <v>1.02</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E125" t="n">
         <v>-0.07000000000000001</v>
@@ -3728,25 +3728,25 @@
         <v>2.08</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.71</v>
+        <v>-0.74</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G126" t="n">
         <v>-0.09</v>
       </c>
       <c r="H126" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="127">
@@ -3757,19 +3757,19 @@
         <v>3.21</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.84</v>
+        <v>-0.87</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.37</v>
+        <v>-0.39</v>
       </c>
       <c r="F127" t="n">
         <v>-0.06</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="H127" t="n">
         <v>0.05</v>
@@ -3786,19 +3786,19 @@
         <v>4.43</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="H128" t="n">
         <v>0.05</v>
@@ -3812,22 +3812,22 @@
         <v>5</v>
       </c>
       <c r="B129" t="n">
-        <v>5.78</v>
+        <v>5.77</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.04</v>
+        <v>-1.15</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.75</v>
+        <v>-0.77</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="H129" t="n">
         <v>0.05</v>
@@ -3893,31 +3893,31 @@
         <v>1</v>
       </c>
       <c r="B132" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="C132" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="D132" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="E132" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="F132" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="H132" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.9</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="133">
@@ -3925,31 +3925,31 @@
         <v>2</v>
       </c>
       <c r="B133" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="C133" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E133" t="n">
         <v>1.49</v>
       </c>
-      <c r="D133" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E133" t="n">
-        <v>1.51</v>
-      </c>
       <c r="F133" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="H133" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.25</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="134">
@@ -3957,31 +3957,31 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="C134" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="D134" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="E134" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="F134" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.22</v>
+        <v>-0.05</v>
       </c>
       <c r="H134" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="I134" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.97</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="135">
@@ -3989,31 +3989,31 @@
         <v>4</v>
       </c>
       <c r="B135" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="C135" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="D135" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="E135" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="F135" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.28</v>
+        <v>-0.09</v>
       </c>
       <c r="H135" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.09</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="136">
@@ -4021,31 +4021,31 @@
         <v>5</v>
       </c>
       <c r="B136" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="C136" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="D136" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="E136" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="F136" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.33</v>
+        <v>-0.11</v>
       </c>
       <c r="H136" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="I136" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.59</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="139">
@@ -4107,16 +4107,16 @@
         <v>1</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.42</v>
+        <v>-0.38</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="F141" t="n">
         <v>-0</v>
@@ -4125,10 +4125,10 @@
         <v>0.04</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="I141" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="142">
@@ -4136,28 +4136,28 @@
         <v>2</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.6</v>
+        <v>-0.51</v>
       </c>
       <c r="F142" t="n">
         <v>-0</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="143">
@@ -4165,28 +4165,28 @@
         <v>3</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.33</v>
+        <v>-0.28</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.65</v>
+        <v>-0.55</v>
       </c>
       <c r="F143" t="n">
         <v>-0</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.11</v>
+        <v>-0.16</v>
       </c>
       <c r="I143" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -4194,28 +4194,28 @@
         <v>4</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.33</v>
+        <v>-0.3</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.66</v>
+        <v>-0.55</v>
       </c>
       <c r="F144" t="n">
         <v>-0</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="I144" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="145">
@@ -4223,28 +4223,28 @@
         <v>5</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.1</v>
+        <v>-0.31</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.67</v>
+        <v>-0.55</v>
       </c>
       <c r="F145" t="n">
         <v>-0</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="I145" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="147">
@@ -4302,10 +4302,10 @@
         <v>-0</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="E148" t="n">
         <v>0.16</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I148" t="n">
         <v>-0.02</v>
@@ -4331,19 +4331,19 @@
         <v>-0.01</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="E149" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F149" t="n">
         <v>-0.02</v>
       </c>
       <c r="G149" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H149" t="n">
         <v>0.02</v>
@@ -4360,19 +4360,19 @@
         <v>-0.02</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="H150" t="n">
         <v>0.02</v>
@@ -4389,16 +4389,16 @@
         <v>-0.03</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="G151" t="n">
         <v>-0.09</v>
@@ -4418,19 +4418,19 @@
         <v>-0.04</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="H152" t="n">
         <v>0.01</v>
@@ -4496,31 +4496,31 @@
         <v>1</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.67</v>
+        <v>-0.62</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.57</v>
+        <v>-0.53</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="H155" t="n">
-        <v>-0.28</v>
+        <v>-0.22</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="J155" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="156">
@@ -4528,31 +4528,31 @@
         <v>2</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.68</v>
+        <v>-0.63</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.51</v>
+        <v>-0.46</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.32</v>
+        <v>-0.21</v>
       </c>
       <c r="J156" t="n">
-        <v>1.47</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="157">
@@ -4560,31 +4560,31 @@
         <v>3</v>
       </c>
       <c r="B157" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.87</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="E157" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I157" t="n">
         <v>-0.23</v>
       </c>
-      <c r="F157" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="G157" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H157" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I157" t="n">
-        <v>-0.37</v>
-      </c>
       <c r="J157" t="n">
-        <v>1.99</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="158">
@@ -4592,31 +4592,31 @@
         <v>4</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.55</v>
+        <v>-0.53</v>
       </c>
       <c r="C158" t="n">
-        <v>-1.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.29</v>
+        <v>-0.23</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.71</v>
+        <v>-0.63</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.41</v>
+        <v>-0.26</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="J158" t="n">
-        <v>2.42</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="159">
@@ -4624,31 +4624,31 @@
         <v>5</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="C159" t="n">
-        <v>-1.07</v>
+        <v>-1.01</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.74</v>
+        <v>-0.65</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.4</v>
+        <v>-0.25</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="J159" t="n">
-        <v>2.84</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="162">
@@ -4710,16 +4710,16 @@
         <v>1</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="C164" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>-1.32</v>
+        <v>-1.01</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="F164" t="n">
         <v>-0</v>
@@ -4739,16 +4739,16 @@
         <v>2</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="C165" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D165" t="n">
-        <v>-2.23</v>
+        <v>-1.68</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.54</v>
+        <v>-0.52</v>
       </c>
       <c r="F165" t="n">
         <v>-0</v>
@@ -4757,10 +4757,10 @@
         <v>-0.14</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="166">
@@ -4768,16 +4768,16 @@
         <v>3</v>
       </c>
       <c r="B166" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="C166" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="D166" t="n">
-        <v>-2.84</v>
+        <v>-2.15</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="F166" t="n">
         <v>-0</v>
@@ -4786,10 +4786,10 @@
         <v>-0.13</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="167">
@@ -4797,16 +4797,16 @@
         <v>4</v>
       </c>
       <c r="B167" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="C167" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="D167" t="n">
-        <v>-3.3</v>
+        <v>-2.51</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="F167" t="n">
         <v>-0</v>
@@ -4815,7 +4815,7 @@
         <v>-0.12</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="I167" t="n">
         <v>-0.71</v>
@@ -4826,16 +4826,16 @@
         <v>5</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="C168" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="D168" t="n">
-        <v>-3.7</v>
+        <v>-2.82</v>
       </c>
       <c r="E168" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="F168" t="n">
         <v>-0</v>
@@ -4844,10 +4844,10 @@
         <v>-0.11</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="170">
@@ -4905,7 +4905,7 @@
         <v>-0.01</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="D171" t="n">
         <v>-0.04</v>
@@ -4920,10 +4920,10 @@
         <v>0.97</v>
       </c>
       <c r="H171" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="172">
@@ -4931,22 +4931,22 @@
         <v>2</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.34</v>
+        <v>-0.29</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H172" t="n">
         <v>0.02</v>
@@ -4960,22 +4960,22 @@
         <v>3</v>
       </c>
       <c r="B173" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H173" t="n">
         <v>0.02</v>
@@ -4989,22 +4989,22 @@
         <v>4</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.25</v>
+        <v>-0.21</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.24</v>
+        <v>-0.21</v>
       </c>
       <c r="F174" t="n">
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H174" t="n">
         <v>0.01</v>
@@ -5018,28 +5018,28 @@
         <v>5</v>
       </c>
       <c r="B175" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D175" t="n">
         <v>-0.25</v>
       </c>
-      <c r="C175" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="E175" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="F175" t="n">
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I175" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="177">
@@ -5099,31 +5099,31 @@
         <v>1</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.6</v>
+        <v>-0.52</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F178" t="n">
         <v>-0.11</v>
       </c>
       <c r="G178" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H178" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I178" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="H178" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="I178" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="J178" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="179">
@@ -5131,31 +5131,31 @@
         <v>2</v>
       </c>
       <c r="B179" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
       <c r="C179" t="n">
-        <v>-1</v>
+        <v>-0.88</v>
       </c>
       <c r="D179" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.34</v>
+        <v>-0.29</v>
       </c>
       <c r="F179" t="n">
         <v>-0.25</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="J179" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="180">
@@ -5163,31 +5163,31 @@
         <v>3</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.58</v>
+        <v>-0.49</v>
       </c>
       <c r="C180" t="n">
-        <v>-1.17</v>
+        <v>-1.05</v>
       </c>
       <c r="D180" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.49</v>
+        <v>-0.42</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.59</v>
+        <v>-0.42</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.27</v>
+        <v>-0.12</v>
       </c>
       <c r="J180" t="n">
-        <v>2.82</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="181">
@@ -5195,31 +5195,31 @@
         <v>4</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.63</v>
+        <v>-0.55</v>
       </c>
       <c r="C181" t="n">
-        <v>-1.27</v>
+        <v>-1.15</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.58</v>
+        <v>-0.51</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.72</v>
+        <v>-0.54</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="J181" t="n">
-        <v>3.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="182">
@@ -5227,31 +5227,31 @@
         <v>5</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.66</v>
+        <v>-0.59</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.31</v>
+        <v>-1.2</v>
       </c>
       <c r="D182" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="E182" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F182" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G182" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H182" t="n">
         <v>-0.65</v>
       </c>
-      <c r="F182" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="G182" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H182" t="n">
-        <v>-0.84</v>
-      </c>
       <c r="I182" t="n">
-        <v>-0.24</v>
+        <v>-0.09</v>
       </c>
       <c r="J182" t="n">
-        <v>5.06</v>
+        <v>3.63</v>
       </c>
     </row>
   </sheetData>
@@ -10189,25 +10189,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0.02</v>
       </c>
       <c r="D3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.01</v>
       </c>
       <c r="I3" t="n">
         <v>0.02</v>
@@ -10218,25 +10218,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.03</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.02</v>
       </c>
       <c r="I4" t="n">
         <v>-0.06</v>
@@ -10253,10 +10253,10 @@
         <v>-0.01</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -10265,10 +10265,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -10279,13 +10279,13 @@
         <v>0.02</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
         <v>-0</v>
@@ -10294,7 +10294,7 @@
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0.08</v>
@@ -10305,16 +10305,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -10323,7 +10323,7 @@
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0.01</v>
@@ -10384,13 +10384,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
         <v>-0.03</v>
@@ -10399,7 +10399,7 @@
         <v>-0.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -10413,10 +10413,10 @@
         <v>-0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>-0.01</v>
@@ -10425,13 +10425,13 @@
         <v>0.03</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -10445,7 +10445,7 @@
         <v>-0.01</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
         <v>-0</v>
@@ -10471,10 +10471,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>-0</v>
@@ -10483,13 +10483,13 @@
         <v>-0.04</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="H13" t="n">
         <v>-0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -10500,22 +10500,22 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
         <v>0.01</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
@@ -10581,28 +10581,28 @@
         <v>0.03</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="D17" t="n">
         <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
         <v>-0.02</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="18">
@@ -10610,13 +10610,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="C18" t="n">
         <v>-0.02</v>
       </c>
-      <c r="C18" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="D18" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E18" t="n">
         <v>-0.01</v>
@@ -10625,16 +10625,16 @@
         <v>-0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="H18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I18" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I18" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
@@ -10642,31 +10642,31 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="C19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J19" t="n">
         <v>-0.02</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.34</v>
       </c>
     </row>
     <row r="20">
@@ -10677,28 +10677,28 @@
         <v>0.02</v>
       </c>
       <c r="C20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.02</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="H20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J20" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.42</v>
       </c>
     </row>
     <row r="21">
@@ -10706,31 +10706,31 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.02</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.01</v>
-      </c>
       <c r="D21" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="J21" t="n">
-        <v>0.55</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="24">
@@ -10792,25 +10792,25 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>-0.02</v>
       </c>
       <c r="D26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H26" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.01</v>
       </c>
       <c r="I26" t="n">
         <v>0.02</v>
@@ -10821,28 +10821,28 @@
         <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="G27" t="n">
         <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="28">
@@ -10850,28 +10850,28 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
         <v>-0.02</v>
       </c>
-      <c r="C28" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="D28" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.44</v>
+        <v>0.08</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="29">
@@ -10879,28 +10879,28 @@
         <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="C29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E29" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D29" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="F29" t="n">
-        <v>-0.47</v>
+        <v>0.1</v>
       </c>
       <c r="G29" t="n">
         <v>0.02</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="30">
@@ -10908,25 +10908,25 @@
         <v>5</v>
       </c>
       <c r="B30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C30" t="n">
         <v>-0.02</v>
       </c>
-      <c r="C30" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="D30" t="n">
-        <v>-0.17</v>
+        <v>0.1</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>0.13</v>
@@ -10987,13 +10987,13 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F33" t="n">
         <v>-0.03</v>
@@ -11002,7 +11002,7 @@
         <v>-0.03</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>-0</v>
@@ -11016,22 +11016,22 @@
         <v>-0</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0.01</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>-0</v>
@@ -11045,22 +11045,22 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0.02</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -11074,22 +11074,22 @@
         <v>-0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="D36" t="n">
         <v>0.03</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" t="n">
         <v>-0.02</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>-0</v>
@@ -11103,25 +11103,25 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G37" t="n">
         <v>-0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="39">
@@ -11184,28 +11184,28 @@
         <v>0.03</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="D40" t="n">
         <v>-0.05</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F40" t="n">
         <v>-0.02</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J40" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="41">
@@ -11213,31 +11213,31 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.02</v>
       </c>
-      <c r="C41" t="n">
+      <c r="G41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H41" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D41" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.02</v>
-      </c>
       <c r="I41" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="J41" t="n">
-        <v>0.19</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="42">
@@ -11245,31 +11245,31 @@
         <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F42" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.01</v>
-      </c>
       <c r="I42" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="43">
@@ -11277,31 +11277,31 @@
         <v>4</v>
       </c>
       <c r="B43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E43" t="n">
         <v>0.02</v>
       </c>
-      <c r="C43" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="F43" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J43" t="n">
-        <v>0.67</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="44">
@@ -11309,31 +11309,31 @@
         <v>5</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="E44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I44" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.01</v>
-      </c>
       <c r="J44" t="n">
-        <v>0.99</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="47">
@@ -11401,10 +11401,10 @@
         <v>0.01</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -11413,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="I49" t="n">
         <v>-0.01</v>
@@ -11430,10 +11430,10 @@
         <v>0.02</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -11442,10 +11442,10 @@
         <v>-0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="51">
@@ -11453,16 +11453,16 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C51" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="E51" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>-0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I51" t="n">
         <v>0.01</v>
@@ -11482,25 +11482,25 @@
         <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="C52" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D52" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="E52" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.04</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.14</v>
       </c>
       <c r="I52" t="n">
         <v>-0.02</v>
@@ -11511,25 +11511,25 @@
         <v>5</v>
       </c>
       <c r="B53" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D53" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="E53" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H53" t="n">
         <v>0.03</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.19</v>
       </c>
       <c r="I53" t="n">
         <v>-0.04</v>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D56" t="n">
         <v>0.01</v>
@@ -11631,13 +11631,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H57" t="n">
         <v>-0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="58">
@@ -11648,13 +11648,13 @@
         <v>0.01</v>
       </c>
       <c r="C58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D58" t="n">
         <v>0.04</v>
       </c>
-      <c r="D58" t="n">
-        <v>0.03</v>
-      </c>
       <c r="E58" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F58" t="n">
         <v>0.01</v>
@@ -11663,7 +11663,7 @@
         <v>-0.02</v>
       </c>
       <c r="H58" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>-0</v>
@@ -11677,16 +11677,16 @@
         <v>0.01</v>
       </c>
       <c r="C59" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="D59" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G59" t="n">
         <v>-0.01</v>
@@ -11695,7 +11695,7 @@
         <v>-0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="60">
@@ -11706,25 +11706,25 @@
         <v>0.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="D60" t="n">
         <v>0.05</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="62">
@@ -11784,10 +11784,10 @@
         <v>1</v>
       </c>
       <c r="B63" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C63" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D63" t="n">
         <v>0.01</v>
@@ -11799,16 +11799,16 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H63" t="n">
         <v>-0.02</v>
       </c>
-      <c r="H63" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="I63" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="64">
@@ -11819,28 +11819,28 @@
         <v>0.05</v>
       </c>
       <c r="C64" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E64" t="n">
         <v>0.03</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.89</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="65">
@@ -11851,28 +11851,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D65" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E65" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.35</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="66">
@@ -11880,31 +11880,31 @@
         <v>4</v>
       </c>
       <c r="B66" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D66" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E66" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F66" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G66" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I66" t="n">
         <v>-0.06</v>
       </c>
-      <c r="H66" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="J66" t="n">
-        <v>-1.81</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="67">
@@ -11912,31 +11912,31 @@
         <v>5</v>
       </c>
       <c r="B67" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="C67" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="D67" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="E67" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="F67" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G67" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I67" t="n">
         <v>-0.06</v>
       </c>
-      <c r="H67" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="J67" t="n">
-        <v>-2.26</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="70">
@@ -11998,25 +11998,25 @@
         <v>1</v>
       </c>
       <c r="B72" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C72" t="n">
         <v>0.05</v>
       </c>
       <c r="D72" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E72" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="F72" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I72" t="n">
         <v>-0.02</v>
@@ -12027,25 +12027,25 @@
         <v>2</v>
       </c>
       <c r="B73" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="C73" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D73" t="n">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="E73" t="n">
         <v>0.16</v>
       </c>
       <c r="F73" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I73" t="n">
         <v>0.02</v>
@@ -12056,25 +12056,25 @@
         <v>3</v>
       </c>
       <c r="B74" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C74" t="n">
         <v>0.06</v>
       </c>
-      <c r="C74" t="n">
-        <v>0.1</v>
-      </c>
       <c r="D74" t="n">
-        <v>0.26</v>
+        <v>-0.02</v>
       </c>
       <c r="E74" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F74" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>-0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="I74" t="n">
         <v>-0.03</v>
@@ -12085,28 +12085,28 @@
         <v>4</v>
       </c>
       <c r="B75" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="C75" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="D75" t="n">
-        <v>0.36</v>
+        <v>-0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="F75" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>-0.02</v>
       </c>
       <c r="H75" t="n">
-        <v>0.19</v>
+        <v>-0.02</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -12114,16 +12114,16 @@
         <v>5</v>
       </c>
       <c r="B76" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="C76" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="D76" t="n">
-        <v>0.44</v>
+        <v>-0.1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -12132,10 +12132,10 @@
         <v>-0.02</v>
       </c>
       <c r="H76" t="n">
-        <v>0.25</v>
+        <v>-0.03</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="78">
@@ -12193,13 +12193,13 @@
         <v>-0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F79" t="n">
         <v>0.02</v>
@@ -12211,7 +12211,7 @@
         <v>-0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="80">
@@ -12222,16 +12222,16 @@
         <v>-0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="D80" t="n">
         <v>0.02</v>
       </c>
       <c r="E80" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="G80" t="n">
         <v>-0</v>
@@ -12248,28 +12248,28 @@
         <v>3</v>
       </c>
       <c r="B81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="D81" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E81" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -12277,28 +12277,28 @@
         <v>4</v>
       </c>
       <c r="B82" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="C82" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D82" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E82" t="n">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G82" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -12306,28 +12306,28 @@
         <v>5</v>
       </c>
       <c r="B83" t="n">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="D83" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E83" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F83" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G83" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="85">
@@ -12390,28 +12390,28 @@
         <v>0.02</v>
       </c>
       <c r="C86" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D86" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E86" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J86" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I86" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="J86" t="n">
-        <v>-0.1</v>
       </c>
     </row>
     <row r="87">
@@ -12419,31 +12419,31 @@
         <v>2</v>
       </c>
       <c r="B87" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="C87" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="D87" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E87" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>-0.01</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.24</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="88">
@@ -12451,31 +12451,31 @@
         <v>3</v>
       </c>
       <c r="B88" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="C88" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="D88" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="E88" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>-0.02</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="89">
@@ -12483,31 +12483,31 @@
         <v>4</v>
       </c>
       <c r="B89" t="n">
-        <v>0.11</v>
+        <v>-0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="D89" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="E89" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="F89" t="n">
         <v>-0.03</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="90">
@@ -12515,31 +12515,31 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="C90" t="n">
-        <v>0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="D90" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="E90" t="n">
-        <v>0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="F90" t="n">
         <v>-0.04</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.18</v>
+        <v>-0.03</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -12604,10 +12604,10 @@
         <v>0.02</v>
       </c>
       <c r="C95" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D95" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E95" t="n">
         <v>0.06</v>
@@ -12619,7 +12619,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I95" t="n">
         <v>-0.01</v>
@@ -12630,16 +12630,16 @@
         <v>2</v>
       </c>
       <c r="B96" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C96" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D96" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E96" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -12648,10 +12648,10 @@
         <v>-0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="I96" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="97">
@@ -12659,16 +12659,16 @@
         <v>3</v>
       </c>
       <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E97" t="n">
         <v>0.04</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0.06</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -12677,10 +12677,10 @@
         <v>-0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I97" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="98">
@@ -12688,16 +12688,16 @@
         <v>4</v>
       </c>
       <c r="B98" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="C98" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="D98" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="E98" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -12706,7 +12706,7 @@
         <v>-0.01</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>-0.04</v>
@@ -12717,16 +12717,16 @@
         <v>5</v>
       </c>
       <c r="B99" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="C99" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="D99" t="n">
-        <v>0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -12735,7 +12735,7 @@
         <v>-0.01</v>
       </c>
       <c r="H99" t="n">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="I99" t="n">
         <v>-0.03</v>
@@ -12796,7 +12796,7 @@
         <v>-0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D102" t="n">
         <v>0.02</v>
@@ -12811,7 +12811,7 @@
         <v>0.01</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -12825,22 +12825,22 @@
         <v>-0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D103" t="n">
         <v>0.03</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F103" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="H103" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
         <v>-0</v>
@@ -12854,16 +12854,16 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="D104" t="n">
         <v>0.04</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12880,19 +12880,19 @@
         <v>4</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="D105" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="F105" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G105" t="n">
         <v>0.01</v>
@@ -12909,22 +12909,22 @@
         <v>5</v>
       </c>
       <c r="B106" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="D106" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="F106" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>-0</v>
@@ -12990,31 +12990,31 @@
         <v>1</v>
       </c>
       <c r="B109" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C109" t="n">
         <v>0.04</v>
       </c>
       <c r="D109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G109" t="n">
         <v>0.02</v>
       </c>
-      <c r="E109" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F109" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>-0</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J109" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="I109" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J109" t="n">
-        <v>-0.2</v>
       </c>
     </row>
     <row r="110">
@@ -13022,31 +13022,31 @@
         <v>2</v>
       </c>
       <c r="B110" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="C110" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="D110" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E110" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G110" t="n">
         <v>0.03</v>
       </c>
-      <c r="F110" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G110" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="H110" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.35</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="111">
@@ -13054,31 +13054,31 @@
         <v>3</v>
       </c>
       <c r="B111" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="C111" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G111" t="n">
         <v>0.04</v>
       </c>
-      <c r="E111" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F111" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="H111" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.46</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="112">
@@ -13086,31 +13086,31 @@
         <v>4</v>
       </c>
       <c r="B112" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="C112" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D112" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E112" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F112" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="113">
@@ -13118,31 +13118,31 @@
         <v>5</v>
       </c>
       <c r="B113" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="D113" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E113" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E113" t="n">
-        <v>0.04</v>
-      </c>
       <c r="F113" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.64</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="116">
@@ -13204,16 +13204,16 @@
         <v>1</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="C118" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="E118" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -13222,7 +13222,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="I118" t="n">
         <v>0.01</v>
@@ -13233,25 +13233,25 @@
         <v>2</v>
       </c>
       <c r="B119" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C119" t="n">
         <v>0.02</v>
       </c>
-      <c r="C119" t="n">
-        <v>0.04</v>
-      </c>
       <c r="D119" t="n">
-        <v>0.46</v>
+        <v>-0.05</v>
       </c>
       <c r="E119" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -13262,16 +13262,16 @@
         <v>3</v>
       </c>
       <c r="B120" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="C120" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D120" t="n">
-        <v>0.75</v>
+        <v>-0.21</v>
       </c>
       <c r="E120" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -13280,7 +13280,7 @@
         <v>-0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="I120" t="n">
         <v>0.01</v>
@@ -13291,16 +13291,16 @@
         <v>4</v>
       </c>
       <c r="B121" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="C121" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D121" t="n">
-        <v>1.21</v>
+        <v>-0.24</v>
       </c>
       <c r="E121" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -13309,10 +13309,10 @@
         <v>-0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="122">
@@ -13320,16 +13320,16 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="C122" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="D122" t="n">
-        <v>1.69</v>
+        <v>-0.28</v>
       </c>
       <c r="E122" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -13338,10 +13338,10 @@
         <v>-0</v>
       </c>
       <c r="H122" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
@@ -13399,10 +13399,10 @@
         <v>-0</v>
       </c>
       <c r="C125" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -13414,10 +13414,10 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
         <v>-0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -13425,28 +13425,28 @@
         <v>2</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="E126" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -13454,22 +13454,22 @@
         <v>3</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C127" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E127" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G127" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H127" t="n">
         <v>-0.01</v>
@@ -13483,22 +13483,22 @@
         <v>4</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="E128" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F128" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G128" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H128" t="n">
         <v>-0.01</v>
@@ -13512,22 +13512,22 @@
         <v>5</v>
       </c>
       <c r="B129" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="E129" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="G129" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H129" t="n">
         <v>-0.01</v>
@@ -13593,31 +13593,31 @@
         <v>1</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="C132" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D132" t="n">
         <v>-0</v>
       </c>
-      <c r="D132" t="n">
-        <v>0.02</v>
-      </c>
       <c r="E132" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.04</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -13625,31 +13625,31 @@
         <v>2</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="C133" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="D133" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="E133" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F133" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.08</v>
+        <v>-0</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.18</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="134">
@@ -13657,31 +13657,31 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="C134" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="D134" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E134" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F134" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.3</v>
+        <v>-0.13</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="135">
@@ -13689,31 +13689,31 @@
         <v>4</v>
       </c>
       <c r="B135" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="C135" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="D135" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="E135" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F135" t="n">
         <v>0.13</v>
       </c>
-      <c r="F135" t="n">
-        <v>0.06</v>
-      </c>
       <c r="G135" t="n">
-        <v>-0.4</v>
+        <v>-0.21</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.16</v>
+        <v>-0.05</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.98</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="136">
@@ -13721,31 +13721,31 @@
         <v>5</v>
       </c>
       <c r="B136" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E136" t="n">
         <v>0.2</v>
       </c>
-      <c r="C136" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D136" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0.24</v>
-      </c>
       <c r="F136" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.48</v>
+        <v>-0.26</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.35</v>
+        <v>-0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.56</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="139">
@@ -13807,16 +13807,16 @@
         <v>1</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D141" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F141" t="n">
         <v>-0</v>
@@ -13825,10 +13825,10 @@
         <v>-0.08</v>
       </c>
       <c r="H141" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.46</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="142">
@@ -13836,28 +13836,28 @@
         <v>2</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="D142" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="F142" t="n">
         <v>-0</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="H142" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I142" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -13865,28 +13865,28 @@
         <v>3</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D143" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F143" t="n">
         <v>-0</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="144">
@@ -13894,28 +13894,28 @@
         <v>4</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="D144" t="n">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F144" t="n">
         <v>-0</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="145">
@@ -13923,28 +13923,28 @@
         <v>5</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="D145" t="n">
-        <v>0.24</v>
+        <v>0.03</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="F145" t="n">
         <v>-0</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="I145" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="147">
@@ -14002,10 +14002,10 @@
         <v>-0</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="D148" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
         <v>-0.01</v>
@@ -14017,7 +14017,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
         <v>-0.01</v>
@@ -14031,19 +14031,19 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="D149" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H149" t="n">
         <v>0.01</v>
@@ -14060,19 +14060,19 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F150" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G150" t="n">
         <v>-0.02</v>
-      </c>
-      <c r="G150" t="n">
-        <v>-0.01</v>
       </c>
       <c r="H150" t="n">
         <v>0.01</v>
@@ -14089,16 +14089,16 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="D151" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G151" t="n">
         <v>-0.03</v>
@@ -14115,28 +14115,28 @@
         <v>5</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D152" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I152" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -14196,31 +14196,31 @@
         <v>1</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F155" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G155" t="n">
         <v>0.02</v>
       </c>
-      <c r="G155" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="H155" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I155" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J155" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0.23</v>
       </c>
     </row>
     <row r="156">
@@ -14228,31 +14228,31 @@
         <v>2</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="C156" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E156" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D156" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="E156" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
       <c r="F156" t="n">
-        <v>-0.05</v>
+        <v>-0</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="J156" t="n">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="157">
@@ -14260,31 +14260,31 @@
         <v>3</v>
       </c>
       <c r="B157" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F157" t="n">
         <v>-0.03</v>
       </c>
-      <c r="C157" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="D157" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="E157" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="F157" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="G157" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="J157" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="158">
@@ -14292,31 +14292,31 @@
         <v>4</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.15</v>
+        <v>-0.09</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="J158" t="n">
-        <v>1.11</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="159">
@@ -14324,31 +14324,31 @@
         <v>5</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="J159" t="n">
-        <v>1.42</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="162">
@@ -14410,16 +14410,16 @@
         <v>1</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C164" t="n">
         <v>-0.06</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.18</v>
+        <v>0.13</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="F164" t="n">
         <v>-0</v>
@@ -14439,16 +14439,16 @@
         <v>2</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.28</v>
+        <v>0.27</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="F165" t="n">
         <v>-0</v>
@@ -14457,10 +14457,10 @@
         <v>0.05</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="166">
@@ -14468,16 +14468,16 @@
         <v>3</v>
       </c>
       <c r="B166" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.34</v>
+        <v>0.35</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="F166" t="n">
         <v>-0</v>
@@ -14486,10 +14486,10 @@
         <v>0.05</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I166" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="167">
@@ -14497,16 +14497,16 @@
         <v>4</v>
       </c>
       <c r="B167" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.46</v>
+        <v>0.33</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.22</v>
+        <v>-0.29</v>
       </c>
       <c r="F167" t="n">
         <v>-0</v>
@@ -14515,7 +14515,7 @@
         <v>0.05</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I167" t="n">
         <v>0.25</v>
@@ -14526,16 +14526,16 @@
         <v>5</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.6</v>
+        <v>0.28</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.22</v>
+        <v>-0.34</v>
       </c>
       <c r="F168" t="n">
         <v>-0</v>
@@ -14544,10 +14544,10 @@
         <v>0.05</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I168" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="170">
@@ -14602,16 +14602,16 @@
         <v>1</v>
       </c>
       <c r="B171" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D171" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -14620,10 +14620,10 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="172">
@@ -14631,28 +14631,28 @@
         <v>2</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I172" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -14660,22 +14660,22 @@
         <v>3</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H173" t="n">
         <v>-0</v>
@@ -14689,22 +14689,22 @@
         <v>4</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -14718,28 +14718,28 @@
         <v>5</v>
       </c>
       <c r="B175" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I175" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="177">
@@ -14799,31 +14799,31 @@
         <v>1</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C178" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J178" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="D178" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E178" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F178" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G178" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H178" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J178" t="n">
-        <v>0.17</v>
       </c>
     </row>
     <row r="179">
@@ -14831,31 +14831,31 @@
         <v>2</v>
       </c>
       <c r="B179" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F179" t="n">
         <v>-0</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H179" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="J179" t="n">
-        <v>0.46</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="180">
@@ -14863,31 +14863,31 @@
         <v>3</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.03</v>
+        <v>0.14</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>0.82</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="181">
@@ -14895,31 +14895,31 @@
         <v>4</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.12</v>
+        <v>-0</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.22</v>
+        <v>-0.28</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="J181" t="n">
-        <v>1.24</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="182">
@@ -14927,31 +14927,31 @@
         <v>5</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.23</v>
+        <v>-0.33</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F182" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="J182" t="n">
-        <v>1.68</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
